--- a/orthogonal_validation/results/tables/step14_DE_only.xlsx
+++ b/orthogonal_validation/results/tables/step14_DE_only.xlsx
@@ -453,775 +453,775 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>10:41404000</t>
+          <t>ENSMUSG00000117879</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>2310015A16Rik</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>-5.2845</v>
+        <v>3.3752</v>
       </c>
       <c r="D2" t="n">
-        <v>0.017225</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>11:116060000</t>
+          <t>ENSMUSG00000053714</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>4732471J01Rik</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>0.8257</v>
+        <v>-3.7625</v>
       </c>
       <c r="D3" t="n">
-        <v>0.002619</v>
+        <v>0.023211</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>11:5470000</t>
+          <t>ENSMUSG00000044906</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>4930503L19Rik</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>6.1401</v>
+        <v>2.9642</v>
       </c>
       <c r="D4" t="n">
-        <v>0.000672</v>
+        <v>0.005953</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>11:83463000</t>
+          <t>ENSMUSG00000121494</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>9030619P08Rik</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>1.0772</v>
+        <v>1.6797</v>
       </c>
       <c r="D5" t="n">
-        <v>0.010641</v>
+        <v>0.010612</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>12:104360000</t>
+          <t>ENSMUSG00000093483</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>AA465934</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>1.1664</v>
+        <v>3.0148</v>
       </c>
       <c r="D6" t="n">
-        <v>0.029745</v>
+        <v>0.032154</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>12:104361000</t>
+          <t>ENSMUSG00000031333</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Abcb7</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>1.7688</v>
+        <v>-3.1629</v>
       </c>
       <c r="D7" t="n">
-        <v>0.001884</v>
+        <v>0.026379</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>14:30625000</t>
+          <t>ENSMUSG00000028127</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Abcd3</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>1.9458</v>
+        <v>-0.7958</v>
       </c>
       <c r="D8" t="n">
-        <v>0.013112</v>
+        <v>0.006155</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>14:46322000</t>
+          <t>ENSMUSG00000032724</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Abtb2</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>1.227</v>
+        <v>-1.0975</v>
       </c>
       <c r="D9" t="n">
-        <v>0</v>
+        <v>0.03964</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>16:30075000</t>
+          <t>ENSMUSG00000020917</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Acly</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>0.5738</v>
+        <v>-1.1604</v>
       </c>
       <c r="D10" t="n">
-        <v>0.000342</v>
+        <v>3e-06</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>16:91882000</t>
+          <t>ENSMUSG00000062825</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Actg1</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>-2.3586</v>
+        <v>0.8794</v>
       </c>
       <c r="D11" t="n">
-        <v>0.043947</v>
+        <v>0.000848</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>17:85372000</t>
+          <t>ENSMUSG00000029106</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Add1</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>1.4365</v>
+        <v>0.6263</v>
       </c>
       <c r="D12" t="n">
-        <v>0.001886</v>
+        <v>0.029745</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>18:20799000</t>
+          <t>ENSMUSG00000121473</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Adh6-ps1</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>-1.4435</v>
+        <v>-1.3358</v>
       </c>
       <c r="D13" t="n">
-        <v>0</v>
+        <v>0.006178</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>19:39595000</t>
+          <t>ENSMUSG00000026272</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Agxt</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>-1.1657</v>
+        <v>0.8429</v>
       </c>
       <c r="D14" t="n">
-        <v>1e-05</v>
+        <v>6e-06</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>19:5506000</t>
+          <t>ENSMUSG00000020288</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Ahsa2</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>0.9461000000000001</v>
+        <v>-0.7499</v>
       </c>
       <c r="D15" t="n">
-        <v>6.2e-05</v>
+        <v>0.000428</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>1:151012000</t>
+          <t>ENSMUSG00000033715</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Akr1c14</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>4.9601</v>
+        <v>-0.7353</v>
       </c>
       <c r="D16" t="n">
-        <v>0</v>
+        <v>0.037176</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>1:151017000</t>
+          <t>ENSMUSG00000071551</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Akr1c19</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>-1.3225</v>
+        <v>-2.2414</v>
       </c>
       <c r="D17" t="n">
-        <v>0.029494</v>
+        <v>0.000226</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>1:160830000</t>
+          <t>ENSMUSG00000072115</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Ang</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>-0.5406</v>
+        <v>1.3453</v>
       </c>
       <c r="D18" t="n">
-        <v>0.039971</v>
+        <v>1e-05</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>1:21334000</t>
+          <t>ENSMUSG00000032231</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Anxa2</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>-6.7023</v>
+        <v>0.9702</v>
       </c>
       <c r="D19" t="n">
-        <v>1e-06</v>
+        <v>0.010776</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2:22479000</t>
+          <t>ENSMUSG00000063558</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Aox1</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>3.5133</v>
+        <v>-1.2065</v>
       </c>
       <c r="D20" t="n">
-        <v>0.009585</v>
+        <v>0.010722</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2:58680000</t>
+          <t>ENSMUSG00000030762</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Aqp8</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>1.1413</v>
+        <v>-1.1892</v>
       </c>
       <c r="D21" t="n">
-        <v>0.025449</v>
+        <v>6.600000000000001e-05</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>3:40743000</t>
+          <t>ENSMUSG00000057315</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Arhgap24</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>-1.1448</v>
+        <v>-0.9619</v>
       </c>
       <c r="D22" t="n">
-        <v>0.012227</v>
+        <v>0.044533</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>3:82938000</t>
+          <t>ENSMUSG00000030047</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Arhgap25</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>0.982</v>
+        <v>1.8753</v>
       </c>
       <c r="D23" t="n">
-        <v>0.006696</v>
+        <v>0.002789</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>4:144938000</t>
+          <t>ENSMUSG00000040964</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Arhgef10l</t>
         </is>
       </c>
       <c r="C24" t="n">
-        <v>5.1477</v>
+        <v>0.8807</v>
       </c>
       <c r="D24" t="n">
-        <v>0.042349</v>
+        <v>0.038152</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>4:152416000</t>
+          <t>ENSMUSG00000015522</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Arnt</t>
         </is>
       </c>
       <c r="C25" t="n">
-        <v>0.7151999999999999</v>
+        <v>0.7625999999999999</v>
       </c>
       <c r="D25" t="n">
-        <v>0.01052</v>
+        <v>0.028855</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>4:61968000</t>
+          <t>ENSMUSG00000055116</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Arntl</t>
         </is>
       </c>
       <c r="C26" t="n">
-        <v>-2.3074</v>
+        <v>-1.5653</v>
       </c>
       <c r="D26" t="n">
-        <v>0.034848</v>
+        <v>0</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>4:6264000</t>
+          <t>ENSMUSG00000024121</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Atp6v0c</t>
         </is>
       </c>
       <c r="C27" t="n">
-        <v>-1.3771</v>
+        <v>-11.5966</v>
       </c>
       <c r="D27" t="n">
-        <v>0.005365</v>
+        <v>0.000381</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>5:113234000</t>
+          <t>ENSMUSG00000028238</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Atp6v0d2</t>
         </is>
       </c>
       <c r="C28" t="n">
-        <v>0.6432</v>
+        <v>3.4982</v>
       </c>
       <c r="D28" t="n">
-        <v>0.001644</v>
+        <v>0.038568</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>7:25924000</t>
+          <t>ENSMUSG00000026630</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Batf3</t>
         </is>
       </c>
       <c r="C29" t="n">
-        <v>7.4302</v>
+        <v>1.4543</v>
       </c>
       <c r="D29" t="n">
-        <v>2.5e-05</v>
+        <v>0.029673</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>7:33900000</t>
+          <t>ENSMUSG00000027792</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Bche</t>
         </is>
       </c>
       <c r="C30" t="n">
-        <v>-0.8692</v>
+        <v>-3.7597</v>
       </c>
       <c r="D30" t="n">
-        <v>2e-06</v>
+        <v>0.000137</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>7:99306000</t>
+          <t>ENSMUSG00000049658</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Bdp1</t>
         </is>
       </c>
       <c r="C31" t="n">
-        <v>3.8699</v>
+        <v>-1.9488</v>
       </c>
       <c r="D31" t="n">
-        <v>0.002164</v>
+        <v>0.019032</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>8:129179000</t>
+          <t>ENSMUSG00000061132</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Blnk</t>
         </is>
       </c>
       <c r="C32" t="n">
-        <v>1.3992</v>
+        <v>3.1226</v>
       </c>
       <c r="D32" t="n">
-        <v>0.015745</v>
+        <v>0</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>8:91613000</t>
+          <t>ENSMUSG00000024335</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Brd2</t>
         </is>
       </c>
       <c r="C33" t="n">
-        <v>0.9946</v>
+        <v>-0.5326</v>
       </c>
       <c r="D33" t="n">
-        <v>0.033505</v>
+        <v>0.004575</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>9:107526000</t>
+          <t>ENSMUSG00000020423</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Btg2</t>
         </is>
       </c>
       <c r="C34" t="n">
-        <v>0.7813</v>
+        <v>2.0901</v>
       </c>
       <c r="D34" t="n">
-        <v>0.005649</v>
+        <v>0</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>9:107551000</t>
+          <t>ENSMUSG00000024371</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>C2</t>
         </is>
       </c>
       <c r="C35" t="n">
-        <v>3.5042</v>
+        <v>0.7538</v>
       </c>
       <c r="D35" t="n">
-        <v>0</v>
+        <v>3.9e-05</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>9:110814000</t>
+          <t>ENSMUSG00000024164</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>C3</t>
         </is>
       </c>
       <c r="C36" t="n">
-        <v>-9.4314</v>
+        <v>0.6870000000000001</v>
       </c>
       <c r="D36" t="n">
-        <v>0</v>
+        <v>0.003854</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>9:46140000</t>
+          <t>ENSMUSG00000073418</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>C4b</t>
         </is>
       </c>
       <c r="C37" t="n">
-        <v>0.9224</v>
+        <v>0.7601</v>
       </c>
       <c r="D37" t="n">
-        <v>0.000218</v>
+        <v>0.007243</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>ENSMUSG00000000326</t>
+          <t>ENSMUSG00000102095</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Comt</t>
+          <t>C730036E19Rik</t>
         </is>
       </c>
       <c r="C38" t="n">
-        <v>-0.6262</v>
+        <v>-5.2658</v>
       </c>
       <c r="D38" t="n">
-        <v>0.012701</v>
+        <v>0.004986</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>ENSMUSG00000000594</t>
+          <t>ENSMUSG00000014226</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Gm2a</t>
+          <t>Cacybp</t>
         </is>
       </c>
       <c r="C39" t="n">
-        <v>-0.6975</v>
+        <v>-1.0205</v>
       </c>
       <c r="D39" t="n">
-        <v>0.026621</v>
+        <v>4e-05</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>ENSMUSG00000000628</t>
+          <t>ENSMUSG00000053819</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Hk2</t>
+          <t>Camk2d</t>
         </is>
       </c>
       <c r="C40" t="n">
-        <v>1.4892</v>
+        <v>-3.3588</v>
       </c>
       <c r="D40" t="n">
-        <v>0.033328</v>
+        <v>0.003916</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>ENSMUSG00000001138</t>
+          <t>ENSMUSG00000038357</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Cnnm3</t>
+          <t>Camp</t>
         </is>
       </c>
       <c r="C41" t="n">
-        <v>-1.2979</v>
+        <v>6.4288</v>
       </c>
       <c r="D41" t="n">
-        <v>0.021382</v>
+        <v>0.002789</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>ENSMUSG00000002265</t>
+          <t>ENSMUSG00000031641</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Peg3</t>
+          <t>Cbr4</t>
         </is>
       </c>
       <c r="C42" t="n">
-        <v>-2.0382</v>
+        <v>1.1178</v>
       </c>
       <c r="D42" t="n">
-        <v>0.026829</v>
+        <v>0.003616</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>ENSMUSG00000002699</t>
+          <t>ENSMUSG00000029385</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Lcp2</t>
+          <t>Ccng2</t>
         </is>
       </c>
       <c r="C43" t="n">
-        <v>3.5842</v>
+        <v>-0.8656</v>
       </c>
       <c r="D43" t="n">
-        <v>0.017377</v>
+        <v>0.013777</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>ENSMUSG00000003053</t>
+          <t>ENSMUSG00000015854</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Cyp2c29</t>
+          <t>Cd5l</t>
         </is>
       </c>
       <c r="C44" t="n">
-        <v>-0.6944</v>
+        <v>0.989</v>
       </c>
       <c r="D44" t="n">
-        <v>0.026441</v>
+        <v>0.01449</v>
       </c>
     </row>
     <row r="45">
@@ -1245,1024 +1245,1024 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>ENSMUSG00000003762</t>
+          <t>ENSMUSG00000066149</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Coq8b</t>
+          <t>Cdc26</t>
         </is>
       </c>
       <c r="C46" t="n">
-        <v>1.143</v>
+        <v>-4.729</v>
       </c>
       <c r="D46" t="n">
-        <v>0.00993</v>
+        <v>0.000147</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>ENSMUSG00000003868</t>
+          <t>ENSMUSG00000056501</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Ruvbl2</t>
+          <t>Cebpb</t>
         </is>
       </c>
       <c r="C47" t="n">
-        <v>-2.053</v>
+        <v>0.6631</v>
       </c>
       <c r="D47" t="n">
-        <v>0.000677</v>
+        <v>0.000647</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>ENSMUSG00000004038</t>
+          <t>ENSMUSG00000071637</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Gstm3</t>
+          <t>Cebpd</t>
         </is>
       </c>
       <c r="C48" t="n">
-        <v>-2.3062</v>
+        <v>1.5735</v>
       </c>
       <c r="D48" t="n">
-        <v>0</v>
+        <v>0.000327</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>ENSMUSG00000004098</t>
+          <t>ENSMUSG00000044066</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Col5a3</t>
+          <t>Cep68</t>
         </is>
       </c>
       <c r="C49" t="n">
-        <v>-1.2378</v>
+        <v>-1.0223</v>
       </c>
       <c r="D49" t="n">
-        <v>0.000515</v>
+        <v>0.036795</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>ENSMUSG00000004552</t>
+          <t>ENSMUSG00000057074</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Ctse</t>
+          <t>Ces1g</t>
         </is>
       </c>
       <c r="C50" t="n">
-        <v>7.0444</v>
+        <v>0.6133999999999999</v>
       </c>
       <c r="D50" t="n">
-        <v>0</v>
+        <v>0.000846</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>ENSMUSG00000004951</t>
+          <t>ENSMUSG00000055730</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Hspb1</t>
+          <t>Ces2a</t>
         </is>
       </c>
       <c r="C51" t="n">
-        <v>-2.0176</v>
+        <v>-1.0885</v>
       </c>
       <c r="D51" t="n">
-        <v>0</v>
+        <v>0.001193</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>ENSMUSG00000005268</t>
+          <t>ENSMUSG00000061825</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Prlr</t>
+          <t>Ces2c</t>
         </is>
       </c>
       <c r="C52" t="n">
-        <v>0.9199000000000001</v>
+        <v>-1.4872</v>
       </c>
       <c r="D52" t="n">
-        <v>0.043947</v>
+        <v>0.03964</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>ENSMUSG00000005514</t>
+          <t>ENSMUSG00000090231</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Por</t>
+          <t>Cfb</t>
         </is>
       </c>
       <c r="C53" t="n">
-        <v>0.7701</v>
+        <v>0.6953</v>
       </c>
       <c r="D53" t="n">
-        <v>0.00436</v>
+        <v>0.007775</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>ENSMUSG00000005547</t>
+          <t>ENSMUSG00000058952</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Cyp2a5</t>
+          <t>Cfi</t>
         </is>
       </c>
       <c r="C54" t="n">
-        <v>-1.275</v>
+        <v>0.6591</v>
       </c>
       <c r="D54" t="n">
-        <v>3e-06</v>
+        <v>0.00112</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>ENSMUSG00000006014</t>
+          <t>ENSMUSG00000038550</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Prg4</t>
+          <t>Ciart</t>
         </is>
       </c>
       <c r="C55" t="n">
-        <v>1.2553</v>
+        <v>2.2746</v>
       </c>
       <c r="D55" t="n">
-        <v>0.005212</v>
+        <v>9.6e-05</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>ENSMUSG00000006522</t>
+          <t>ENSMUSG00000039910</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Itih3</t>
+          <t>Cited2</t>
         </is>
       </c>
       <c r="C56" t="n">
-        <v>1.4339</v>
+        <v>-0.661</v>
       </c>
       <c r="D56" t="n">
-        <v>0.000368</v>
+        <v>0.044836</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>ENSMUSG00000006529</t>
+          <t>ENSMUSG00000029238</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Itih1</t>
+          <t>Clock</t>
         </is>
       </c>
       <c r="C57" t="n">
-        <v>0.527</v>
+        <v>-1.1807</v>
       </c>
       <c r="D57" t="n">
-        <v>1.1e-05</v>
+        <v>0.004116</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>ENSMUSG00000008200</t>
+          <t>ENSMUSG00000015357</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Fnbp4</t>
+          <t>Clpx</t>
         </is>
       </c>
       <c r="C58" t="n">
-        <v>-0.8429</v>
+        <v>-0.7274</v>
       </c>
       <c r="D58" t="n">
-        <v>0.013777</v>
+        <v>0.00495</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>ENSMUSG00000009687</t>
+          <t>ENSMUSG00000001138</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Fxyd5</t>
+          <t>Cnnm3</t>
         </is>
       </c>
       <c r="C59" t="n">
-        <v>1.0699</v>
+        <v>-1.2979</v>
       </c>
       <c r="D59" t="n">
-        <v>0.006308</v>
+        <v>0.021382</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>ENSMUSG00000010064</t>
+          <t>ENSMUSG00000045672</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Slc38a3</t>
+          <t>Col27a1</t>
         </is>
       </c>
       <c r="C60" t="n">
-        <v>0.7902</v>
+        <v>-1.3706</v>
       </c>
       <c r="D60" t="n">
-        <v>0</v>
+        <v>0.000218</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>ENSMUSG00000014226</t>
+          <t>ENSMUSG00000004098</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Cacybp</t>
+          <t>Col5a3</t>
         </is>
       </c>
       <c r="C61" t="n">
-        <v>-1.0205</v>
+        <v>-1.2378</v>
       </c>
       <c r="D61" t="n">
-        <v>4e-05</v>
+        <v>0.000515</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>ENSMUSG00000015357</t>
+          <t>ENSMUSG00000000326</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Clpx</t>
+          <t>Comt</t>
         </is>
       </c>
       <c r="C62" t="n">
-        <v>-0.7274</v>
+        <v>-0.6262</v>
       </c>
       <c r="D62" t="n">
-        <v>0.00495</v>
+        <v>0.012701</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>ENSMUSG00000015522</t>
+          <t>ENSMUSG00000025981</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Arnt</t>
+          <t>Coq10b</t>
         </is>
       </c>
       <c r="C63" t="n">
-        <v>0.7625999999999999</v>
+        <v>0.641</v>
       </c>
       <c r="D63" t="n">
-        <v>0.028855</v>
+        <v>0.025898</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>ENSMUSG00000015854</t>
+          <t>ENSMUSG00000003762</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Cd5l</t>
+          <t>Coq8b</t>
         </is>
       </c>
       <c r="C64" t="n">
-        <v>0.989</v>
+        <v>1.143</v>
       </c>
       <c r="D64" t="n">
-        <v>0.01449</v>
+        <v>0.00993</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>ENSMUSG00000016024</t>
+          <t>ENSMUSG00000024900</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Lbp</t>
+          <t>Cpt1a</t>
         </is>
       </c>
       <c r="C65" t="n">
-        <v>0.9477</v>
+        <v>0.5284</v>
       </c>
       <c r="D65" t="n">
-        <v>0.000789</v>
+        <v>0.021382</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>ENSMUSG00000016409</t>
+          <t>ENSMUSG00000020038</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Nkap</t>
+          <t>Cry1</t>
         </is>
       </c>
       <c r="C66" t="n">
-        <v>-1.1426</v>
+        <v>-1.8554</v>
       </c>
       <c r="D66" t="n">
-        <v>0.013688</v>
+        <v>0</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>ENSMUSG00000017057</t>
+          <t>ENSMUSG00000023044</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Il13ra1</t>
+          <t>Csad</t>
         </is>
       </c>
       <c r="C67" t="n">
-        <v>1.1676</v>
+        <v>-2.5634</v>
       </c>
       <c r="D67" t="n">
-        <v>0.003444</v>
+        <v>0</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>ENSMUSG00000018102</t>
+          <t>ENSMUSG00000032482</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>H2bc4</t>
+          <t>Cspg5</t>
         </is>
       </c>
       <c r="C68" t="n">
-        <v>-0.5386</v>
+        <v>-3.3384</v>
       </c>
       <c r="D68" t="n">
-        <v>0.00689</v>
+        <v>0.025569</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>ENSMUSG00000019139</t>
+          <t>ENSMUSG00000060034</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Isyna1</t>
+          <t>Ctf2</t>
         </is>
       </c>
       <c r="C69" t="n">
-        <v>2.0257</v>
+        <v>-6.0188</v>
       </c>
       <c r="D69" t="n">
-        <v>0.034907</v>
+        <v>0.0115</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>ENSMUSG00000019461</t>
+          <t>ENSMUSG00000030560</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Plscr3</t>
+          <t>Ctsc</t>
         </is>
       </c>
       <c r="C70" t="n">
-        <v>1.1052</v>
+        <v>0.6385</v>
       </c>
       <c r="D70" t="n">
-        <v>0.007732</v>
+        <v>0.026978</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>ENSMUSG00000019590</t>
+          <t>ENSMUSG00000004552</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Cyb561</t>
+          <t>Ctse</t>
         </is>
       </c>
       <c r="C71" t="n">
-        <v>1.5149</v>
+        <v>7.0444</v>
       </c>
       <c r="D71" t="n">
-        <v>0.020196</v>
+        <v>0</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>ENSMUSG00000019737</t>
+          <t>ENSMUSG00000029380</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Syne4</t>
+          <t>Cxcl1</t>
         </is>
       </c>
       <c r="C72" t="n">
-        <v>3.9237</v>
+        <v>4.3195</v>
       </c>
       <c r="D72" t="n">
-        <v>0</v>
+        <v>2.1e-05</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>ENSMUSG00000019823</t>
+          <t>ENSMUSG00000023078</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Mical1</t>
+          <t>Cxcl13</t>
         </is>
       </c>
       <c r="C73" t="n">
-        <v>2.4681</v>
+        <v>2.4513</v>
       </c>
       <c r="D73" t="n">
-        <v>0.029123</v>
+        <v>0</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>ENSMUSG00000019916</t>
+          <t>ENSMUSG00000019590</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>P4ha1</t>
+          <t>Cyb561</t>
         </is>
       </c>
       <c r="C74" t="n">
-        <v>-0.844</v>
+        <v>1.5149</v>
       </c>
       <c r="D74" t="n">
-        <v>0.029268</v>
+        <v>0.020196</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>ENSMUSG00000020017</t>
+          <t>ENSMUSG00000032310</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Hal</t>
+          <t>Cyp1a2</t>
         </is>
       </c>
       <c r="C75" t="n">
-        <v>0.6347</v>
+        <v>-1.0117</v>
       </c>
       <c r="D75" t="n">
-        <v>0.024058</v>
+        <v>0.004986</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>ENSMUSG00000020038</t>
+          <t>ENSMUSG00000005547</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Cry1</t>
+          <t>Cyp2a5</t>
         </is>
       </c>
       <c r="C76" t="n">
-        <v>-1.8554</v>
+        <v>-1.275</v>
       </c>
       <c r="D76" t="n">
-        <v>0</v>
+        <v>3e-06</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>ENSMUSG00000020232</t>
+          <t>ENSMUSG00000040660</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Hmg20b</t>
+          <t>Cyp2b9</t>
         </is>
       </c>
       <c r="C77" t="n">
-        <v>-0.646</v>
+        <v>5.7992</v>
       </c>
       <c r="D77" t="n">
-        <v>0.002756</v>
+        <v>0</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>ENSMUSG00000020288</t>
+          <t>ENSMUSG00000003053</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Ahsa2</t>
+          <t>Cyp2c29</t>
         </is>
       </c>
       <c r="C78" t="n">
-        <v>-0.7499</v>
+        <v>-0.6944</v>
       </c>
       <c r="D78" t="n">
-        <v>0.000428</v>
+        <v>0.026441</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>ENSMUSG00000020423</t>
+          <t>ENSMUSG00000067225</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Btg2</t>
+          <t>Cyp2c54</t>
         </is>
       </c>
       <c r="C79" t="n">
-        <v>2.0901</v>
+        <v>0.8713</v>
       </c>
       <c r="D79" t="n">
-        <v>0</v>
+        <v>0.002286</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>ENSMUSG00000020427</t>
+          <t>ENSMUSG00000025002</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Igfbp3</t>
+          <t>Cyp2c55</t>
         </is>
       </c>
       <c r="C80" t="n">
-        <v>0.5659</v>
+        <v>-1.715</v>
       </c>
       <c r="D80" t="n">
-        <v>0.033423</v>
+        <v>0.02535</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>ENSMUSG00000020634</t>
+          <t>ENSMUSG00000068086</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Ubxn2a</t>
+          <t>Cyp2d9</t>
         </is>
       </c>
       <c r="C81" t="n">
-        <v>-0.6092</v>
+        <v>-1.2312</v>
       </c>
       <c r="D81" t="n">
-        <v>0.002179</v>
+        <v>0.019509</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>ENSMUSG00000020642</t>
+          <t>ENSMUSG00000066071</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Rnf144a</t>
+          <t>Cyp4a12a</t>
         </is>
       </c>
       <c r="C82" t="n">
-        <v>-1.6495</v>
+        <v>-2.009</v>
       </c>
       <c r="D82" t="n">
-        <v>0.044533</v>
+        <v>0.045033</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>ENSMUSG00000020733</t>
+          <t>ENSMUSG00000048440</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Slc9a3r1</t>
+          <t>Cyp4f16</t>
         </is>
       </c>
       <c r="C83" t="n">
-        <v>0.6091</v>
+        <v>1.7204</v>
       </c>
       <c r="D83" t="n">
-        <v>0.007624</v>
+        <v>0.016931</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>ENSMUSG00000020776</t>
+          <t>ENSMUSG00000028240</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Fbf1</t>
+          <t>Cyp7a1</t>
         </is>
       </c>
       <c r="C84" t="n">
-        <v>1.3418</v>
+        <v>-2.7434</v>
       </c>
       <c r="D84" t="n">
-        <v>0.036795</v>
+        <v>0</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>ENSMUSG00000020805</t>
+          <t>ENSMUSG00000073609</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Slc13a5</t>
+          <t>D2hgdh</t>
         </is>
       </c>
       <c r="C85" t="n">
-        <v>6.4684</v>
+        <v>-1.14</v>
       </c>
       <c r="D85" t="n">
-        <v>0.000395</v>
+        <v>0.032154</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>ENSMUSG00000020889</t>
+          <t>ENSMUSG00000039168</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Nr1d1</t>
+          <t>Dap</t>
         </is>
       </c>
       <c r="C86" t="n">
-        <v>2.7088</v>
+        <v>0.5135999999999999</v>
       </c>
       <c r="D86" t="n">
-        <v>0</v>
+        <v>0.005069</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>ENSMUSG00000020917</t>
+          <t>ENSMUSG00000028194</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Acly</t>
+          <t>Ddah1</t>
         </is>
       </c>
       <c r="C87" t="n">
-        <v>-1.1604</v>
+        <v>-1.436</v>
       </c>
       <c r="D87" t="n">
-        <v>3e-06</v>
+        <v>0.001651</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>ENSMUSG00000021091</t>
+          <t>ENSMUSG00000056268</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Serpina3n</t>
+          <t>Dennd1b</t>
         </is>
       </c>
       <c r="C88" t="n">
-        <v>1.6712</v>
+        <v>-2.5936</v>
       </c>
       <c r="D88" t="n">
-        <v>0.000428</v>
+        <v>0.017727</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>ENSMUSG00000021190</t>
+          <t>ENSMUSG00000048489</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Lgmn</t>
+          <t>Depp1</t>
         </is>
       </c>
       <c r="C89" t="n">
-        <v>0.7138</v>
+        <v>0.9267</v>
       </c>
       <c r="D89" t="n">
-        <v>0.017535</v>
+        <v>0.002988</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>ENSMUSG00000021270</t>
+          <t>ENSMUSG00000026502</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Hsp90aa1</t>
+          <t>Desi2</t>
         </is>
       </c>
       <c r="C90" t="n">
-        <v>-1.0236</v>
+        <v>-0.9392</v>
       </c>
       <c r="D90" t="n">
-        <v>0.028327</v>
+        <v>0.033263</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>ENSMUSG00000021392</t>
+          <t>ENSMUSG00000034926</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Nol8</t>
+          <t>Dhcr24</t>
         </is>
       </c>
       <c r="C91" t="n">
-        <v>-1.4926</v>
+        <v>0.5749</v>
       </c>
       <c r="D91" t="n">
-        <v>0.046254</v>
+        <v>0.032929</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>ENSMUSG00000021510</t>
+          <t>ENSMUSG00000030986</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Zfp729a</t>
+          <t>Dhx32</t>
         </is>
       </c>
       <c r="C92" t="n">
-        <v>-4.1645</v>
+        <v>0.9012</v>
       </c>
       <c r="D92" t="n">
-        <v>0.001651</v>
+        <v>0.004221</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>ENSMUSG00000021775</t>
+          <t>ENSMUSG00000036764</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>Nr1d2</t>
+          <t>Dnajc12</t>
         </is>
       </c>
       <c r="C93" t="n">
-        <v>2.3108</v>
+        <v>1.6567</v>
       </c>
       <c r="D93" t="n">
-        <v>0.001548</v>
+        <v>0.034793</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>ENSMUSG00000021876</t>
+          <t>ENSMUSG00000034774</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>Rnase4</t>
+          <t>Dsg1c</t>
         </is>
       </c>
       <c r="C94" t="n">
-        <v>0.8047</v>
+        <v>3.1588</v>
       </c>
       <c r="D94" t="n">
-        <v>0.007048</v>
+        <v>0</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>ENSMUSG00000021922</t>
+          <t>ENSMUSG00000038418</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>Itih4</t>
+          <t>Egr1</t>
         </is>
       </c>
       <c r="C95" t="n">
-        <v>0.8555</v>
+        <v>3.191</v>
       </c>
       <c r="D95" t="n">
-        <v>0.009526</v>
+        <v>0.039949</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>ENSMUSG00000021957</t>
+          <t>ENSMUSG00000028445</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>Tkt</t>
+          <t>Enho</t>
         </is>
       </c>
       <c r="C96" t="n">
-        <v>-0.6192</v>
+        <v>2.2875</v>
       </c>
       <c r="D96" t="n">
-        <v>0.000967</v>
+        <v>2e-05</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>ENSMUSG00000022032</t>
+          <t>ENSMUSG00000038776</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>Scara5</t>
+          <t>Ephx1</t>
         </is>
       </c>
       <c r="C97" t="n">
-        <v>1.7102</v>
+        <v>-0.9754</v>
       </c>
       <c r="D97" t="n">
-        <v>0.025569</v>
+        <v>0.005529</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>ENSMUSG00000022092</t>
+          <t>ENSMUSG00000040857</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>Ppp3cc</t>
+          <t>Erf</t>
         </is>
       </c>
       <c r="C98" t="n">
-        <v>1.5896</v>
+        <v>0.6855</v>
       </c>
       <c r="D98" t="n">
-        <v>0.00106</v>
+        <v>0.018549</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>ENSMUSG00000022094</t>
+          <t>ENSMUSG00000039958</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>Slc39a14</t>
+          <t>Etfbkmt</t>
         </is>
       </c>
       <c r="C99" t="n">
-        <v>0.7171999999999999</v>
+        <v>-0.781</v>
       </c>
       <c r="D99" t="n">
-        <v>0.037622</v>
+        <v>0.008577</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>ENSMUSG00000022346</t>
+          <t>ENSMUSG00000064254</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>Myc</t>
+          <t>Ethe1</t>
         </is>
       </c>
       <c r="C100" t="n">
-        <v>-3.1808</v>
+        <v>-0.602</v>
       </c>
       <c r="D100" t="n">
-        <v>0.012009</v>
+        <v>0.006389</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>ENSMUSG00000022389</t>
+          <t>ENSMUSG00000041930</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>Tef</t>
+          <t>Fam222a</t>
         </is>
       </c>
       <c r="C101" t="n">
-        <v>0.6037</v>
+        <v>-1.4331</v>
       </c>
       <c r="D101" t="n">
-        <v>0.038152</v>
+        <v>0.000712</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>ENSMUSG00000022540</t>
+          <t>ENSMUSG00000055884</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>Rogdi</t>
+          <t>Fancm</t>
         </is>
       </c>
       <c r="C102" t="n">
-        <v>1.29</v>
+        <v>-3.0269</v>
       </c>
       <c r="D102" t="n">
         <v>6.2e-05</v>
@@ -2271,34 +2271,34 @@
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>ENSMUSG00000022579</t>
+          <t>ENSMUSG00000020776</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>Gpihbp1</t>
+          <t>Fbf1</t>
         </is>
       </c>
       <c r="C103" t="n">
-        <v>0.5377999999999999</v>
+        <v>1.3418</v>
       </c>
       <c r="D103" t="n">
-        <v>0.04916</v>
+        <v>0.036795</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>ENSMUSG00000022707</t>
+          <t>ENSMUSG00000022871</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>Gbe1</t>
+          <t>Fetub</t>
         </is>
       </c>
       <c r="C104" t="n">
-        <v>-1.0916</v>
+        <v>0.6528</v>
       </c>
       <c r="D104" t="n">
         <v>0</v>
@@ -2307,1132 +2307,1132 @@
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>ENSMUSG00000022871</t>
+          <t>ENSMUSG00000028001</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>Fetub</t>
+          <t>Fga</t>
         </is>
       </c>
       <c r="C105" t="n">
-        <v>0.6528</v>
+        <v>0.9442</v>
       </c>
       <c r="D105" t="n">
-        <v>0</v>
+        <v>0.002789</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>ENSMUSG00000022875</t>
+          <t>ENSMUSG00000033831</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>Kng1</t>
+          <t>Fgb</t>
         </is>
       </c>
       <c r="C106" t="n">
-        <v>0.5944</v>
+        <v>0.9001</v>
       </c>
       <c r="D106" t="n">
-        <v>0.013437</v>
+        <v>0.004241</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>ENSMUSG00000022877</t>
+          <t>ENSMUSG00000031565</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>Hrg</t>
+          <t>Fgfr1</t>
         </is>
       </c>
       <c r="C107" t="n">
-        <v>0.6371</v>
+        <v>1.3609</v>
       </c>
       <c r="D107" t="n">
-        <v>0.005892</v>
+        <v>0.036821</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>ENSMUSG00000023033</t>
+          <t>ENSMUSG00000033860</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>Scn8a</t>
+          <t>Fgg</t>
         </is>
       </c>
       <c r="C108" t="n">
-        <v>2.7323</v>
+        <v>0.8889</v>
       </c>
       <c r="D108" t="n">
-        <v>0.000263</v>
+        <v>0.003052</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>ENSMUSG00000023043</t>
+          <t>ENSMUSG00000031594</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>Krt18</t>
+          <t>Fgl1</t>
         </is>
       </c>
       <c r="C109" t="n">
-        <v>0.7346</v>
+        <v>2.0769</v>
       </c>
       <c r="D109" t="n">
-        <v>0.008577</v>
+        <v>0</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>ENSMUSG00000023044</t>
+          <t>ENSMUSG00000032643</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>Csad</t>
+          <t>Fhl3</t>
         </is>
       </c>
       <c r="C110" t="n">
-        <v>-2.5634</v>
+        <v>1.6354</v>
       </c>
       <c r="D110" t="n">
-        <v>0</v>
+        <v>0.017377</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>ENSMUSG00000023078</t>
+          <t>ENSMUSG00000030357</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>Cxcl13</t>
+          <t>Fkbp4</t>
         </is>
       </c>
       <c r="C111" t="n">
-        <v>2.4513</v>
+        <v>-0.6629</v>
       </c>
       <c r="D111" t="n">
-        <v>0</v>
+        <v>0.001107</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>ENSMUSG00000023150</t>
+          <t>ENSMUSG00000031328</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>Ivns1abp</t>
+          <t>Flna</t>
         </is>
       </c>
       <c r="C112" t="n">
-        <v>-0.8002</v>
+        <v>0.7332</v>
       </c>
       <c r="D112" t="n">
-        <v>0.000396</v>
+        <v>0.039971</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>ENSMUSG00000024029</t>
+          <t>ENSMUSG00000034258</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>Tff3</t>
+          <t>Flvcr2</t>
         </is>
       </c>
       <c r="C113" t="n">
-        <v>4.8649</v>
+        <v>1.6538</v>
       </c>
       <c r="D113" t="n">
-        <v>0</v>
+        <v>0.043688</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>ENSMUSG00000024118</t>
+          <t>ENSMUSG00000026193</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>Tedc2</t>
+          <t>Fn1</t>
         </is>
       </c>
       <c r="C114" t="n">
-        <v>-0.5558999999999999</v>
+        <v>0.6609</v>
       </c>
       <c r="D114" t="n">
-        <v>0.012504</v>
+        <v>0.014775</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>ENSMUSG00000024121</t>
+          <t>ENSMUSG00000008200</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>Atp6v0c</t>
+          <t>Fnbp4</t>
         </is>
       </c>
       <c r="C115" t="n">
-        <v>-11.5966</v>
+        <v>-0.8429</v>
       </c>
       <c r="D115" t="n">
-        <v>0.000381</v>
+        <v>0.013777</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>ENSMUSG00000024127</t>
+          <t>ENSMUSG00000009687</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>Prepl</t>
+          <t>Fxyd5</t>
         </is>
       </c>
       <c r="C116" t="n">
-        <v>0.945</v>
+        <v>1.0699</v>
       </c>
       <c r="D116" t="n">
-        <v>0.034235</v>
+        <v>0.006308</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>ENSMUSG00000024164</t>
+          <t>ENSMUSG00000022707</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>C3</t>
+          <t>Gbe1</t>
         </is>
       </c>
       <c r="C117" t="n">
-        <v>0.6870000000000001</v>
+        <v>-1.0916</v>
       </c>
       <c r="D117" t="n">
-        <v>0.003854</v>
+        <v>0</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>ENSMUSG00000024335</t>
+          <t>ENSMUSG00000032350</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>Brd2</t>
+          <t>Gclc</t>
         </is>
       </c>
       <c r="C118" t="n">
-        <v>-0.5326</v>
+        <v>-0.7278</v>
       </c>
       <c r="D118" t="n">
-        <v>0.004575</v>
+        <v>0.028855</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>ENSMUSG00000024371</t>
+          <t>ENSMUSG00000028124</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>C2</t>
+          <t>Gclm</t>
         </is>
       </c>
       <c r="C119" t="n">
-        <v>0.7538</v>
+        <v>-0.8070000000000001</v>
       </c>
       <c r="D119" t="n">
-        <v>3.9e-05</v>
+        <v>1e-05</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>ENSMUSG00000024431</t>
+          <t>ENSMUSG00000027865</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>Nr3c1</t>
+          <t>Gdap2</t>
         </is>
       </c>
       <c r="C120" t="n">
-        <v>-1.4757</v>
+        <v>-1.1167</v>
       </c>
       <c r="D120" t="n">
-        <v>0</v>
+        <v>0.019216</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>ENSMUSG00000024785</t>
+          <t>ENSMUSG00000038508</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>Rcl1</t>
+          <t>Gdf15</t>
         </is>
       </c>
       <c r="C121" t="n">
-        <v>0.8954</v>
+        <v>0.9167999999999999</v>
       </c>
       <c r="D121" t="n">
-        <v>0.001055</v>
+        <v>0.021382</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>ENSMUSG00000024900</t>
+          <t>ENSMUSG00000051335</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>Cpt1a</t>
+          <t>Gfod1</t>
         </is>
       </c>
       <c r="C122" t="n">
-        <v>0.5284</v>
+        <v>-4.7222</v>
       </c>
       <c r="D122" t="n">
-        <v>0.021382</v>
+        <v>0.000883</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>ENSMUSG00000024976</t>
+          <t>ENSMUSG00000048000</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>Shoc2</t>
+          <t>Gigyf2</t>
         </is>
       </c>
       <c r="C123" t="n">
-        <v>-1.1441</v>
+        <v>-0.9639</v>
       </c>
       <c r="D123" t="n">
-        <v>0.04916</v>
+        <v>0.002805</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>ENSMUSG00000024986</t>
+          <t>ENSMUSG00000026333</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>Hhex</t>
+          <t>Gin1</t>
         </is>
       </c>
       <c r="C124" t="n">
-        <v>-1.0682</v>
+        <v>-1.1487</v>
       </c>
       <c r="D124" t="n">
-        <v>0.041586</v>
+        <v>0.034907</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>ENSMUSG00000025002</t>
+          <t>ENSMUSG00000046352</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>Cyp2c55</t>
+          <t>Gjb2</t>
         </is>
       </c>
       <c r="C125" t="n">
-        <v>-1.715</v>
+        <v>0.5836</v>
       </c>
       <c r="D125" t="n">
-        <v>0.02535</v>
+        <v>0.000471</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>ENSMUSG00000025017</t>
+          <t>ENSMUSG00000081642</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>Pik3ap1</t>
+          <t>Gm13532</t>
         </is>
       </c>
       <c r="C126" t="n">
-        <v>0.8877</v>
+        <v>1.2203</v>
       </c>
       <c r="D126" t="n">
-        <v>0.002789</v>
+        <v>1.4e-05</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>ENSMUSG00000025036</t>
+          <t>ENSMUSG00000118017</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>Sfxn2</t>
+          <t>Gm29966</t>
         </is>
       </c>
       <c r="C127" t="n">
-        <v>0.5276999999999999</v>
+        <v>-0.8469</v>
       </c>
       <c r="D127" t="n">
-        <v>0.029363</v>
+        <v>0.002916</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>ENSMUSG00000025396</t>
+          <t>ENSMUSG00000000594</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>Hsd17b6</t>
+          <t>Gm2a</t>
         </is>
       </c>
       <c r="C128" t="n">
-        <v>-1.6092</v>
+        <v>-0.6975</v>
       </c>
       <c r="D128" t="n">
-        <v>0</v>
+        <v>0.026621</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>ENSMUSG00000025511</t>
+          <t>ENSMUSG00000114818</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>Tspan4</t>
+          <t>Gm35164</t>
         </is>
       </c>
       <c r="C129" t="n">
-        <v>0.8984</v>
+        <v>3.4839</v>
       </c>
       <c r="D129" t="n">
-        <v>0.002789</v>
+        <v>1e-06</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>ENSMUSG00000025743</t>
+          <t>ENSMUSG00000105837</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>Sdc3</t>
+          <t>Gm35986</t>
         </is>
       </c>
       <c r="C130" t="n">
-        <v>1.3655</v>
+        <v>-1.8463</v>
       </c>
       <c r="D130" t="n">
-        <v>0.004249</v>
+        <v>0.001169</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>ENSMUSG00000025862</t>
+          <t>ENSMUSG00000108763</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>Stag2</t>
+          <t>Gm36028</t>
         </is>
       </c>
       <c r="C131" t="n">
-        <v>-3.9005</v>
+        <v>-1.9149</v>
       </c>
       <c r="D131" t="n">
-        <v>0.031489</v>
+        <v>0.008472</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>ENSMUSG00000025903</t>
+          <t>ENSMUSG00000110156</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>Lypla1</t>
+          <t>Gm42067</t>
         </is>
       </c>
       <c r="C132" t="n">
-        <v>-0.6724</v>
+        <v>-2.0918</v>
       </c>
       <c r="D132" t="n">
-        <v>0.01052</v>
+        <v>0.022701</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>ENSMUSG00000025937</t>
+          <t>ENSMUSG00000079362</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>Lactb2</t>
+          <t>Gm43302</t>
         </is>
       </c>
       <c r="C133" t="n">
-        <v>-0.7982</v>
+        <v>6.4366</v>
       </c>
       <c r="D133" t="n">
-        <v>1e-06</v>
+        <v>0.003796</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>ENSMUSG00000025981</t>
+          <t>ENSMUSG00000110588</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>Coq10b</t>
+          <t>Gm45774</t>
         </is>
       </c>
       <c r="C134" t="n">
-        <v>0.641</v>
+        <v>4.5927</v>
       </c>
       <c r="D134" t="n">
-        <v>0.025898</v>
+        <v>0.004436</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>ENSMUSG00000026117</t>
+          <t>ENSMUSG00000096768</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>Zap70</t>
+          <t>Gm47283</t>
         </is>
       </c>
       <c r="C135" t="n">
-        <v>1.2308</v>
+        <v>3.2947</v>
       </c>
       <c r="D135" t="n">
-        <v>0.004575</v>
+        <v>0</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>ENSMUSG00000026179</t>
+          <t>ENSMUSG00000113047</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>Pnkd</t>
+          <t>Gm47469</t>
         </is>
       </c>
       <c r="C136" t="n">
-        <v>-0.5076000000000001</v>
+        <v>-4.2081</v>
       </c>
       <c r="D136" t="n">
-        <v>0.028914</v>
+        <v>0.034312</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>ENSMUSG00000026193</t>
+          <t>ENSMUSG00000113529</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>Fn1</t>
+          <t>Gm47484</t>
         </is>
       </c>
       <c r="C137" t="n">
-        <v>0.6609</v>
+        <v>-3.0391</v>
       </c>
       <c r="D137" t="n">
-        <v>0.014775</v>
+        <v>0.036882</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>ENSMUSG00000026249</t>
+          <t>ENSMUSG00000109482</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>Serpine2</t>
+          <t>Gm4756</t>
         </is>
       </c>
       <c r="C138" t="n">
-        <v>-2.6966</v>
+        <v>0.6829</v>
       </c>
       <c r="D138" t="n">
-        <v>0.000179</v>
+        <v>0.045438</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>ENSMUSG00000026272</t>
+          <t>ENSMUSG00000111878</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>Agxt</t>
+          <t>Gm47777</t>
         </is>
       </c>
       <c r="C139" t="n">
-        <v>0.8429</v>
+        <v>4.4982</v>
       </c>
       <c r="D139" t="n">
-        <v>6e-06</v>
+        <v>0.004607</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>ENSMUSG00000026277</t>
+          <t>ENSMUSG00000117912</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>Stk25</t>
+          <t>Gm50383</t>
         </is>
       </c>
       <c r="C140" t="n">
-        <v>-1.2442</v>
+        <v>-1.6648</v>
       </c>
       <c r="D140" t="n">
-        <v>0.009344999999999999</v>
+        <v>0.0009940000000000001</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>ENSMUSG00000026315</t>
+          <t>ENSMUSG00000034837</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>Serpinb8</t>
+          <t>Gnat1</t>
         </is>
       </c>
       <c r="C141" t="n">
-        <v>1.6417</v>
+        <v>1.1984</v>
       </c>
       <c r="D141" t="n">
-        <v>0.017727</v>
+        <v>0.003422</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>ENSMUSG00000026333</t>
+          <t>ENSMUSG00000036402</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>Gin1</t>
+          <t>Gng12</t>
         </is>
       </c>
       <c r="C142" t="n">
-        <v>-1.1487</v>
+        <v>-0.6671</v>
       </c>
       <c r="D142" t="n">
-        <v>0.034907</v>
+        <v>0.012009</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>ENSMUSG00000026393</t>
+          <t>ENSMUSG00000037722</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>Nek7</t>
+          <t>Gnpnat1</t>
         </is>
       </c>
       <c r="C143" t="n">
-        <v>-0.7504</v>
+        <v>-1.5099</v>
       </c>
       <c r="D143" t="n">
-        <v>0.013163</v>
+        <v>0.001961</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>ENSMUSG00000026435</t>
+          <t>ENSMUSG00000029314</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>Slc45a3</t>
+          <t>Gpat3</t>
         </is>
       </c>
       <c r="C144" t="n">
-        <v>-0.7477</v>
+        <v>1.5395</v>
       </c>
       <c r="D144" t="n">
-        <v>0.035107</v>
+        <v>0.020675</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>ENSMUSG00000026502</t>
+          <t>ENSMUSG00000022579</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>Desi2</t>
+          <t>Gpihbp1</t>
         </is>
       </c>
       <c r="C145" t="n">
-        <v>-0.9392</v>
+        <v>0.5377999999999999</v>
       </c>
       <c r="D145" t="n">
-        <v>0.033263</v>
+        <v>0.04916</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>ENSMUSG00000026630</t>
+          <t>ENSMUSG00000058135</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>Batf3</t>
+          <t>Gstm1</t>
         </is>
       </c>
       <c r="C146" t="n">
-        <v>1.4543</v>
+        <v>-1.4177</v>
       </c>
       <c r="D146" t="n">
-        <v>0.029673</v>
+        <v>0</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>ENSMUSG00000026643</t>
+          <t>ENSMUSG00000040562</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>Nmt2</t>
+          <t>Gstm2</t>
         </is>
       </c>
       <c r="C147" t="n">
-        <v>-0.779</v>
+        <v>-0.9704</v>
       </c>
       <c r="D147" t="n">
-        <v>0.000727</v>
+        <v>0.026829</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>ENSMUSG00000026778</t>
+          <t>ENSMUSG00000004038</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>Prkcq</t>
+          <t>Gstm3</t>
         </is>
       </c>
       <c r="C148" t="n">
-        <v>2.507</v>
+        <v>-2.3062</v>
       </c>
       <c r="D148" t="n">
-        <v>0.025456</v>
+        <v>0</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>ENSMUSG00000026822</t>
+          <t>ENSMUSG00000068762</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>Lcn2</t>
+          <t>Gstm6</t>
         </is>
       </c>
       <c r="C149" t="n">
-        <v>4.3348</v>
+        <v>-1.0043</v>
       </c>
       <c r="D149" t="n">
-        <v>5.8e-05</v>
+        <v>0.000459</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>ENSMUSG00000026981</t>
+          <t>ENSMUSG00000060803</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>Il1rn</t>
+          <t>Gstp1</t>
         </is>
       </c>
       <c r="C150" t="n">
-        <v>1.9916</v>
+        <v>-1.3267</v>
       </c>
       <c r="D150" t="n">
-        <v>0.034907</v>
+        <v>0.002789</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>ENSMUSG00000026999</t>
+          <t>ENSMUSG00000038155</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>Nup35</t>
+          <t>Gstp2</t>
         </is>
       </c>
       <c r="C151" t="n">
-        <v>-2.5196</v>
+        <v>-6.0092</v>
       </c>
       <c r="D151" t="n">
-        <v>0.040087</v>
+        <v>0.017515</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>ENSMUSG00000027091</t>
+          <t>ENSMUSG00000040464</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>Zc3h15</t>
+          <t>Gtpbp10</t>
         </is>
       </c>
       <c r="C152" t="n">
-        <v>-0.5835</v>
+        <v>-2.2538</v>
       </c>
       <c r="D152" t="n">
-        <v>0.034906</v>
+        <v>0.00043</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>ENSMUSG00000027201</t>
+          <t>ENSMUSG00000018102</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>Myef2</t>
+          <t>H2bc4</t>
         </is>
       </c>
       <c r="C153" t="n">
-        <v>-2.0042</v>
+        <v>-0.5386</v>
       </c>
       <c r="D153" t="n">
-        <v>0.049479</v>
+        <v>0.00689</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>ENSMUSG00000027378</t>
+          <t>ENSMUSG00000020017</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>Nphp1</t>
+          <t>Hal</t>
         </is>
       </c>
       <c r="C154" t="n">
-        <v>1.4616</v>
+        <v>0.6347</v>
       </c>
       <c r="D154" t="n">
-        <v>0.030415</v>
+        <v>0.024058</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>ENSMUSG00000027514</t>
+          <t>ENSMUSG00000067071</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>Zbp1</t>
+          <t>Hes6</t>
         </is>
       </c>
       <c r="C155" t="n">
-        <v>0.907</v>
+        <v>-1.2844</v>
       </c>
       <c r="D155" t="n">
-        <v>0.04916</v>
+        <v>0</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>ENSMUSG00000027615</t>
+          <t>ENSMUSG00000024986</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>Hps3</t>
+          <t>Hhex</t>
         </is>
       </c>
       <c r="C156" t="n">
-        <v>-1.7445</v>
+        <v>-1.0682</v>
       </c>
       <c r="D156" t="n">
-        <v>0.015033</v>
+        <v>0.041586</v>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>ENSMUSG00000027706</t>
+          <t>ENSMUSG00000000628</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>Sec62</t>
+          <t>Hk2</t>
         </is>
       </c>
       <c r="C157" t="n">
-        <v>-0.6302</v>
+        <v>1.4892</v>
       </c>
       <c r="D157" t="n">
-        <v>0.000709</v>
+        <v>0.033328</v>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>ENSMUSG00000027782</t>
+          <t>ENSMUSG00000020232</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>Kpna4</t>
+          <t>Hmg20b</t>
         </is>
       </c>
       <c r="C158" t="n">
-        <v>-1.2396</v>
+        <v>-0.646</v>
       </c>
       <c r="D158" t="n">
-        <v>0.000828</v>
+        <v>0.002756</v>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>ENSMUSG00000027792</t>
+          <t>ENSMUSG00000086054</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>Bche</t>
+          <t>Hnf1aos1</t>
         </is>
       </c>
       <c r="C159" t="n">
-        <v>-3.7597</v>
+        <v>-1.3606</v>
       </c>
       <c r="D159" t="n">
-        <v>0.000137</v>
+        <v>0.015193</v>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>ENSMUSG00000027865</t>
+          <t>ENSMUSG00000031722</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>Gdap2</t>
+          <t>Hp</t>
         </is>
       </c>
       <c r="C160" t="n">
-        <v>-1.1167</v>
+        <v>1.486</v>
       </c>
       <c r="D160" t="n">
-        <v>0.019216</v>
+        <v>0.003578</v>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>ENSMUSG00000028001</t>
+          <t>ENSMUSG00000027615</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>Fga</t>
+          <t>Hps3</t>
         </is>
       </c>
       <c r="C161" t="n">
-        <v>0.9442</v>
+        <v>-1.7445</v>
       </c>
       <c r="D161" t="n">
-        <v>0.002789</v>
+        <v>0.015033</v>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>ENSMUSG00000028124</t>
+          <t>ENSMUSG00000030895</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>Gclm</t>
+          <t>Hpx</t>
         </is>
       </c>
       <c r="C162" t="n">
-        <v>-0.8070000000000001</v>
+        <v>1.3362</v>
       </c>
       <c r="D162" t="n">
-        <v>1e-05</v>
+        <v>0.002916</v>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>ENSMUSG00000028127</t>
+          <t>ENSMUSG00000022877</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>Abcd3</t>
+          <t>Hrg</t>
         </is>
       </c>
       <c r="C163" t="n">
-        <v>-0.7958</v>
+        <v>0.6371</v>
       </c>
       <c r="D163" t="n">
-        <v>0.006155</v>
+        <v>0.005892</v>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>ENSMUSG00000028150</t>
+          <t>ENSMUSG00000025396</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>Rorc</t>
+          <t>Hsd17b6</t>
         </is>
       </c>
       <c r="C164" t="n">
-        <v>-0.7258</v>
+        <v>-1.6092</v>
       </c>
       <c r="D164" t="n">
-        <v>0.022253</v>
+        <v>0</v>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>ENSMUSG00000028194</t>
+          <t>ENSMUSG00000021270</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>Ddah1</t>
+          <t>Hsp90aa1</t>
         </is>
       </c>
       <c r="C165" t="n">
-        <v>-1.436</v>
+        <v>-1.0236</v>
       </c>
       <c r="D165" t="n">
-        <v>0.001651</v>
+        <v>0.028327</v>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>ENSMUSG00000028238</t>
+          <t>ENSMUSG00000090877</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>Atp6v0d2</t>
+          <t>Hspa1b</t>
         </is>
       </c>
       <c r="C166" t="n">
-        <v>3.4982</v>
+        <v>-0.9762</v>
       </c>
       <c r="D166" t="n">
-        <v>0.038568</v>
+        <v>0.002005</v>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>ENSMUSG00000028240</t>
+          <t>ENSMUSG00000004951</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>Cyp7a1</t>
+          <t>Hspb1</t>
         </is>
       </c>
       <c r="C167" t="n">
-        <v>-2.7434</v>
+        <v>-2.0176</v>
       </c>
       <c r="D167" t="n">
         <v>0</v>
@@ -3441,1420 +3441,1420 @@
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>ENSMUSG00000028359</t>
+          <t>ENSMUSG00000039745</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>Orm3</t>
+          <t>Htatip2</t>
         </is>
       </c>
       <c r="C168" t="n">
-        <v>4.2992</v>
+        <v>-0.7983</v>
       </c>
       <c r="D168" t="n">
-        <v>0</v>
+        <v>0.002988</v>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>ENSMUSG00000028445</t>
+          <t>ENSMUSG00000053560</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>Enho</t>
+          <t>Ier2</t>
         </is>
       </c>
       <c r="C169" t="n">
-        <v>2.2875</v>
+        <v>0.7547</v>
       </c>
       <c r="D169" t="n">
-        <v>2e-05</v>
+        <v>0.038152</v>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>ENSMUSG00000028494</t>
+          <t>ENSMUSG00000020427</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>Plin2</t>
+          <t>Igfbp3</t>
         </is>
       </c>
       <c r="C170" t="n">
-        <v>0.6223</v>
+        <v>0.5659</v>
       </c>
       <c r="D170" t="n">
-        <v>0.026379</v>
+        <v>0.033423</v>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>ENSMUSG00000028555</t>
+          <t>ENSMUSG00000095079</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>Ttc39a</t>
+          <t>Igha</t>
         </is>
       </c>
       <c r="C171" t="n">
-        <v>2.9232</v>
+        <v>3.2498</v>
       </c>
       <c r="D171" t="n">
-        <v>0.020085</v>
+        <v>1.8e-05</v>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>ENSMUSG00000028639</t>
+          <t>ENSMUSG00000076614</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>Ybx1</t>
+          <t>Ighg1</t>
         </is>
       </c>
       <c r="C172" t="n">
-        <v>-0.707</v>
+        <v>3.4313</v>
       </c>
       <c r="D172" t="n">
-        <v>0.041041</v>
+        <v>0.005524</v>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>ENSMUSG00000028744</t>
+          <t>ENSMUSG00000076613</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>Slc66a1</t>
+          <t>Ighg2b</t>
         </is>
       </c>
       <c r="C173" t="n">
-        <v>0.9434</v>
+        <v>3.7499</v>
       </c>
       <c r="D173" t="n">
-        <v>0.026718</v>
+        <v>0</v>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>ENSMUSG00000028849</t>
+          <t>ENSMUSG00000076612</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>Map7d1</t>
+          <t>Ighg2c</t>
         </is>
       </c>
       <c r="C174" t="n">
-        <v>0.6835</v>
+        <v>3.8731</v>
       </c>
       <c r="D174" t="n">
-        <v>0.008869</v>
+        <v>0</v>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>ENSMUSG00000028957</t>
+          <t>ENSMUSG00000076609</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>Per3</t>
+          <t>Igkc</t>
         </is>
       </c>
       <c r="C175" t="n">
-        <v>2.0869</v>
+        <v>3.0166</v>
       </c>
       <c r="D175" t="n">
-        <v>5e-06</v>
+        <v>0</v>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>ENSMUSG00000029106</t>
+          <t>ENSMUSG00000105906</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>Add1</t>
+          <t>Iglc1</t>
         </is>
       </c>
       <c r="C176" t="n">
-        <v>0.6263</v>
+        <v>2.5617</v>
       </c>
       <c r="D176" t="n">
-        <v>0.029745</v>
+        <v>0.021382</v>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>ENSMUSG00000029186</t>
+          <t>ENSMUSG00000017057</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>Pi4k2b</t>
+          <t>Il13ra1</t>
         </is>
       </c>
       <c r="C177" t="n">
-        <v>-0.7049</v>
+        <v>1.1676</v>
       </c>
       <c r="D177" t="n">
-        <v>0.023389</v>
+        <v>0.003444</v>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>ENSMUSG00000029238</t>
+          <t>ENSMUSG00000026981</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>Clock</t>
+          <t>Il1rn</t>
         </is>
       </c>
       <c r="C178" t="n">
-        <v>-1.1807</v>
+        <v>1.9916</v>
       </c>
       <c r="D178" t="n">
-        <v>0.004116</v>
+        <v>0.034907</v>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>ENSMUSG00000029304</t>
+          <t>ENSMUSG00000040612</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>Spp1</t>
+          <t>Ildr2</t>
         </is>
       </c>
       <c r="C179" t="n">
-        <v>1.267</v>
+        <v>0.9314</v>
       </c>
       <c r="D179" t="n">
-        <v>0.001788</v>
+        <v>0.004242</v>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>ENSMUSG00000029314</t>
+          <t>ENSMUSG00000038894</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>Gpat3</t>
+          <t>Irs2</t>
         </is>
       </c>
       <c r="C180" t="n">
-        <v>1.5395</v>
+        <v>-1.1475</v>
       </c>
       <c r="D180" t="n">
-        <v>0.020675</v>
+        <v>2.8e-05</v>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>ENSMUSG00000029380</t>
+          <t>ENSMUSG00000019139</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>Cxcl1</t>
+          <t>Isyna1</t>
         </is>
       </c>
       <c r="C181" t="n">
-        <v>4.3195</v>
+        <v>2.0257</v>
       </c>
       <c r="D181" t="n">
-        <v>2.1e-05</v>
+        <v>0.034907</v>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>ENSMUSG00000029385</t>
+          <t>ENSMUSG00000006529</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>Ccng2</t>
+          <t>Itih1</t>
         </is>
       </c>
       <c r="C182" t="n">
-        <v>-0.8656</v>
+        <v>0.527</v>
       </c>
       <c r="D182" t="n">
-        <v>0.013777</v>
+        <v>1.1e-05</v>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>ENSMUSG00000029597</t>
+          <t>ENSMUSG00000006522</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>Sds</t>
+          <t>Itih3</t>
         </is>
       </c>
       <c r="C183" t="n">
-        <v>1.1685</v>
+        <v>1.4339</v>
       </c>
       <c r="D183" t="n">
-        <v>0.01044</v>
+        <v>0.000368</v>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>ENSMUSG00000029810</t>
+          <t>ENSMUSG00000021922</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>Tmem176b</t>
+          <t>Itih4</t>
         </is>
       </c>
       <c r="C184" t="n">
-        <v>0.8260999999999999</v>
+        <v>0.8555</v>
       </c>
       <c r="D184" t="n">
-        <v>0.001258</v>
+        <v>0.009526</v>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>ENSMUSG00000030004</t>
+          <t>ENSMUSG00000023150</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>Nat8</t>
+          <t>Ivns1abp</t>
         </is>
       </c>
       <c r="C185" t="n">
-        <v>1.3492</v>
+        <v>-0.8002</v>
       </c>
       <c r="D185" t="n">
-        <v>1.1e-05</v>
+        <v>0.000396</v>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>ENSMUSG00000030047</t>
+          <t>ENSMUSG00000052837</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>Arhgap25</t>
+          <t>Junb</t>
         </is>
       </c>
       <c r="C186" t="n">
-        <v>1.8753</v>
+        <v>1.6567</v>
       </c>
       <c r="D186" t="n">
-        <v>0.002789</v>
+        <v>4.4e-05</v>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>ENSMUSG00000030357</t>
+          <t>ENSMUSG00000071076</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>Fkbp4</t>
+          <t>Jund</t>
         </is>
       </c>
       <c r="C187" t="n">
-        <v>-0.6629</v>
+        <v>0.534</v>
       </c>
       <c r="D187" t="n">
-        <v>0.001107</v>
+        <v>0.028953</v>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>ENSMUSG00000030560</t>
+          <t>ENSMUSG00000052726</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>Ctsc</t>
+          <t>Kcnt2</t>
         </is>
       </c>
       <c r="C188" t="n">
-        <v>0.6385</v>
+        <v>5.9137</v>
       </c>
       <c r="D188" t="n">
-        <v>0.026978</v>
+        <v>0.00436</v>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>ENSMUSG00000030579</t>
+          <t>ENSMUSG00000048154</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>Tyrobp</t>
+          <t>Kmt2d</t>
         </is>
       </c>
       <c r="C189" t="n">
-        <v>0.9735</v>
+        <v>-2.1913</v>
       </c>
       <c r="D189" t="n">
-        <v>0.000238</v>
+        <v>0.003023</v>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>ENSMUSG00000030762</t>
+          <t>ENSMUSG00000022875</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>Aqp8</t>
+          <t>Kng1</t>
         </is>
       </c>
       <c r="C190" t="n">
-        <v>-1.1892</v>
+        <v>0.5944</v>
       </c>
       <c r="D190" t="n">
-        <v>6.600000000000001e-05</v>
+        <v>0.013437</v>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>ENSMUSG00000030895</t>
+          <t>ENSMUSG00000060459</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>Hpx</t>
+          <t>Kng2</t>
         </is>
       </c>
       <c r="C191" t="n">
-        <v>1.3362</v>
+        <v>0.6615</v>
       </c>
       <c r="D191" t="n">
-        <v>0.002916</v>
+        <v>0.000883</v>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>ENSMUSG00000030986</t>
+          <t>ENSMUSG00000027782</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>Dhx32</t>
+          <t>Kpna4</t>
         </is>
       </c>
       <c r="C192" t="n">
-        <v>0.9012</v>
+        <v>-1.2396</v>
       </c>
       <c r="D192" t="n">
-        <v>0.004221</v>
+        <v>0.000828</v>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>ENSMUSG00000031328</t>
+          <t>ENSMUSG00000023043</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t>Flna</t>
+          <t>Krt18</t>
         </is>
       </c>
       <c r="C193" t="n">
-        <v>0.7332</v>
+        <v>0.7346</v>
       </c>
       <c r="D193" t="n">
-        <v>0.039971</v>
+        <v>0.008577</v>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>ENSMUSG00000031333</t>
+          <t>ENSMUSG00000049382</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t>Abcb7</t>
+          <t>Krt8</t>
         </is>
       </c>
       <c r="C194" t="n">
-        <v>-3.1629</v>
+        <v>0.7038</v>
       </c>
       <c r="D194" t="n">
-        <v>0.026379</v>
+        <v>0.025989</v>
       </c>
     </row>
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>ENSMUSG00000031565</t>
+          <t>ENSMUSG00000025937</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
         <is>
-          <t>Fgfr1</t>
+          <t>Lactb2</t>
         </is>
       </c>
       <c r="C195" t="n">
-        <v>1.3609</v>
+        <v>-0.7982</v>
       </c>
       <c r="D195" t="n">
-        <v>0.036821</v>
+        <v>1e-06</v>
       </c>
     </row>
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>ENSMUSG00000031594</t>
+          <t>ENSMUSG00000039682</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t>Fgl1</t>
+          <t>Lap3</t>
         </is>
       </c>
       <c r="C196" t="n">
-        <v>2.0769</v>
+        <v>-2.6446</v>
       </c>
       <c r="D196" t="n">
-        <v>0</v>
+        <v>0.027911</v>
       </c>
     </row>
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>ENSMUSG00000031641</t>
+          <t>ENSMUSG00000033499</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
         <is>
-          <t>Cbr4</t>
+          <t>Larp4b</t>
         </is>
       </c>
       <c r="C197" t="n">
-        <v>1.1178</v>
+        <v>-0.5555</v>
       </c>
       <c r="D197" t="n">
-        <v>0.003616</v>
+        <v>0.031885</v>
       </c>
     </row>
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>ENSMUSG00000031715</t>
+          <t>ENSMUSG00000016024</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
         <is>
-          <t>Smarca5</t>
+          <t>Lbp</t>
         </is>
       </c>
       <c r="C198" t="n">
-        <v>-2.5062</v>
+        <v>0.9477</v>
       </c>
       <c r="D198" t="n">
-        <v>0.012227</v>
+        <v>0.000789</v>
       </c>
     </row>
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>ENSMUSG00000031722</t>
+          <t>ENSMUSG00000026822</t>
         </is>
       </c>
       <c r="B199" t="inlineStr">
         <is>
-          <t>Hp</t>
+          <t>Lcn2</t>
         </is>
       </c>
       <c r="C199" t="n">
-        <v>1.486</v>
+        <v>4.3348</v>
       </c>
       <c r="D199" t="n">
-        <v>0.003578</v>
+        <v>5.8e-05</v>
       </c>
     </row>
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t>ENSMUSG00000031762</t>
+          <t>ENSMUSG00000002699</t>
         </is>
       </c>
       <c r="B200" t="inlineStr">
         <is>
-          <t>Mt2</t>
+          <t>Lcp2</t>
         </is>
       </c>
       <c r="C200" t="n">
-        <v>3.7775</v>
+        <v>3.5842</v>
       </c>
       <c r="D200" t="n">
-        <v>1.6e-05</v>
+        <v>0.017377</v>
       </c>
     </row>
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
-          <t>ENSMUSG00000031765</t>
+          <t>ENSMUSG00000036216</t>
         </is>
       </c>
       <c r="B201" t="inlineStr">
         <is>
-          <t>Mt1</t>
+          <t>Leap2</t>
         </is>
       </c>
       <c r="C201" t="n">
-        <v>3.4398</v>
+        <v>-0.5881999999999999</v>
       </c>
       <c r="D201" t="n">
-        <v>0</v>
+        <v>0.012179</v>
       </c>
     </row>
     <row r="202">
       <c r="A202" t="inlineStr">
         <is>
-          <t>ENSMUSG00000031897</t>
+          <t>ENSMUSG00000021190</t>
         </is>
       </c>
       <c r="B202" t="inlineStr">
         <is>
-          <t>Psmb10</t>
+          <t>Lgmn</t>
         </is>
       </c>
       <c r="C202" t="n">
-        <v>0.5258</v>
+        <v>0.7138</v>
       </c>
       <c r="D202" t="n">
-        <v>0.02535</v>
+        <v>0.017535</v>
       </c>
     </row>
     <row r="203">
       <c r="A203" t="inlineStr">
         <is>
-          <t>ENSMUSG00000031939</t>
+          <t>ENSMUSG00000037095</t>
         </is>
       </c>
       <c r="B203" t="inlineStr">
         <is>
-          <t>Taf1d</t>
+          <t>Lrg1</t>
         </is>
       </c>
       <c r="C203" t="n">
-        <v>-0.8745000000000001</v>
+        <v>1.6572</v>
       </c>
       <c r="D203" t="n">
-        <v>0.022153</v>
+        <v>0.000301</v>
       </c>
     </row>
     <row r="204">
       <c r="A204" t="inlineStr">
         <is>
-          <t>ENSMUSG00000032091</t>
+          <t>ENSMUSG00000049988</t>
         </is>
       </c>
       <c r="B204" t="inlineStr">
         <is>
-          <t>Tmprss4</t>
+          <t>Lrrc25</t>
         </is>
       </c>
       <c r="C204" t="n">
-        <v>5.6186</v>
+        <v>1.18</v>
       </c>
       <c r="D204" t="n">
-        <v>0.000145</v>
+        <v>0.030934</v>
       </c>
     </row>
     <row r="205">
       <c r="A205" t="inlineStr">
         <is>
-          <t>ENSMUSG00000032231</t>
+          <t>ENSMUSG00000034158</t>
         </is>
       </c>
       <c r="B205" t="inlineStr">
         <is>
-          <t>Anxa2</t>
+          <t>Lrrc58</t>
         </is>
       </c>
       <c r="C205" t="n">
-        <v>0.9702</v>
+        <v>-0.6676</v>
       </c>
       <c r="D205" t="n">
-        <v>0.010776</v>
+        <v>0.000842</v>
       </c>
     </row>
     <row r="206">
       <c r="A206" t="inlineStr">
         <is>
-          <t>ENSMUSG00000032310</t>
+          <t>ENSMUSG00000025903</t>
         </is>
       </c>
       <c r="B206" t="inlineStr">
         <is>
-          <t>Cyp1a2</t>
+          <t>Lypla1</t>
         </is>
       </c>
       <c r="C206" t="n">
-        <v>-1.0117</v>
+        <v>-0.6724</v>
       </c>
       <c r="D206" t="n">
-        <v>0.004986</v>
+        <v>0.01052</v>
       </c>
     </row>
     <row r="207">
       <c r="A207" t="inlineStr">
         <is>
-          <t>ENSMUSG00000032350</t>
+          <t>ENSMUSG00000033618</t>
         </is>
       </c>
       <c r="B207" t="inlineStr">
         <is>
-          <t>Gclc</t>
+          <t>Map3k13</t>
         </is>
       </c>
       <c r="C207" t="n">
-        <v>-0.7278</v>
+        <v>0.7133</v>
       </c>
       <c r="D207" t="n">
-        <v>0.028855</v>
+        <v>0.014678</v>
       </c>
     </row>
     <row r="208">
       <c r="A208" t="inlineStr">
         <is>
-          <t>ENSMUSG00000032418</t>
+          <t>ENSMUSG00000028849</t>
         </is>
       </c>
       <c r="B208" t="inlineStr">
         <is>
-          <t>Me1</t>
+          <t>Map7d1</t>
         </is>
       </c>
       <c r="C208" t="n">
-        <v>-2.7455</v>
+        <v>0.6835</v>
       </c>
       <c r="D208" t="n">
-        <v>0</v>
+        <v>0.008869</v>
       </c>
     </row>
     <row r="209">
       <c r="A209" t="inlineStr">
         <is>
-          <t>ENSMUSG00000032449</t>
+          <t>ENSMUSG00000063704</t>
         </is>
       </c>
       <c r="B209" t="inlineStr">
         <is>
-          <t>Slc25a36</t>
+          <t>Mapk15</t>
         </is>
       </c>
       <c r="C209" t="n">
-        <v>-3.3359</v>
+        <v>-1.577</v>
       </c>
       <c r="D209" t="n">
-        <v>0.042349</v>
+        <v>0</v>
       </c>
     </row>
     <row r="210">
       <c r="A210" t="inlineStr">
         <is>
-          <t>ENSMUSG00000032482</t>
+          <t>ENSMUSG00000037798</t>
         </is>
       </c>
       <c r="B210" t="inlineStr">
         <is>
-          <t>Cspg5</t>
+          <t>Mat1a</t>
         </is>
       </c>
       <c r="C210" t="n">
-        <v>-3.3384</v>
+        <v>0.6911</v>
       </c>
       <c r="D210" t="n">
-        <v>0.025569</v>
+        <v>0.034907</v>
       </c>
     </row>
     <row r="211">
       <c r="A211" t="inlineStr">
         <is>
-          <t>ENSMUSG00000032501</t>
+          <t>ENSMUSG00000053907</t>
         </is>
       </c>
       <c r="B211" t="inlineStr">
         <is>
-          <t>Trib1</t>
+          <t>Mat2a</t>
         </is>
       </c>
       <c r="C211" t="n">
-        <v>0.6657999999999999</v>
+        <v>0.7126</v>
       </c>
       <c r="D211" t="n">
-        <v>0.002789</v>
+        <v>0.001219</v>
       </c>
     </row>
     <row r="212">
       <c r="A212" t="inlineStr">
         <is>
-          <t>ENSMUSG00000032643</t>
+          <t>ENSMUSG00000032418</t>
         </is>
       </c>
       <c r="B212" t="inlineStr">
         <is>
-          <t>Fhl3</t>
+          <t>Me1</t>
         </is>
       </c>
       <c r="C212" t="n">
-        <v>1.6354</v>
+        <v>-2.7455</v>
       </c>
       <c r="D212" t="n">
-        <v>0.017377</v>
+        <v>0</v>
       </c>
     </row>
     <row r="213">
       <c r="A213" t="inlineStr">
         <is>
-          <t>ENSMUSG00000032724</t>
+          <t>ENSMUSG00000019823</t>
         </is>
       </c>
       <c r="B213" t="inlineStr">
         <is>
-          <t>Abtb2</t>
+          <t>Mical1</t>
         </is>
       </c>
       <c r="C213" t="n">
-        <v>-1.0975</v>
+        <v>2.4681</v>
       </c>
       <c r="D213" t="n">
-        <v>0.03964</v>
+        <v>0.029123</v>
       </c>
     </row>
     <row r="214">
       <c r="A214" t="inlineStr">
         <is>
-          <t>ENSMUSG00000033107</t>
+          <t>ENSMUSG00000035621</t>
         </is>
       </c>
       <c r="B214" t="inlineStr">
         <is>
-          <t>Rnf125</t>
+          <t>Midn</t>
         </is>
       </c>
       <c r="C214" t="n">
-        <v>-0.6397</v>
+        <v>0.8266</v>
       </c>
       <c r="D214" t="n">
-        <v>0.035107</v>
+        <v>0.004986</v>
       </c>
     </row>
     <row r="215">
       <c r="A215" t="inlineStr">
         <is>
-          <t>ENSMUSG00000033499</t>
+          <t>ENSMUSG00000074064</t>
         </is>
       </c>
       <c r="B215" t="inlineStr">
         <is>
-          <t>Larp4b</t>
+          <t>Mlycd</t>
         </is>
       </c>
       <c r="C215" t="n">
-        <v>-0.5555</v>
+        <v>0.5394</v>
       </c>
       <c r="D215" t="n">
-        <v>0.031885</v>
+        <v>0.012227</v>
       </c>
     </row>
     <row r="216">
       <c r="A216" t="inlineStr">
         <is>
-          <t>ENSMUSG00000033618</t>
+          <t>ENSMUSG00000039533</t>
         </is>
       </c>
       <c r="B216" t="inlineStr">
         <is>
-          <t>Map3k13</t>
+          <t>Mmd2</t>
         </is>
       </c>
       <c r="C216" t="n">
-        <v>0.7133</v>
+        <v>3.2568</v>
       </c>
       <c r="D216" t="n">
-        <v>0.014678</v>
+        <v>3.9e-05</v>
       </c>
     </row>
     <row r="217">
       <c r="A217" t="inlineStr">
         <is>
-          <t>ENSMUSG00000033634</t>
+          <t>ENSMUSG00000039616</t>
         </is>
       </c>
       <c r="B217" t="inlineStr">
         <is>
-          <t>Nat8f2</t>
+          <t>Mocos</t>
         </is>
       </c>
       <c r="C217" t="n">
-        <v>0.8129</v>
+        <v>-0.6057</v>
       </c>
       <c r="D217" t="n">
-        <v>0.003702</v>
+        <v>0.047959</v>
       </c>
     </row>
     <row r="218">
       <c r="A218" t="inlineStr">
         <is>
-          <t>ENSMUSG00000033684</t>
+          <t>ENSMUSG00000040269</t>
         </is>
       </c>
       <c r="B218" t="inlineStr">
         <is>
-          <t>Qsox1</t>
+          <t>Mrps28</t>
         </is>
       </c>
       <c r="C218" t="n">
-        <v>0.6951000000000001</v>
+        <v>-1.4618</v>
       </c>
       <c r="D218" t="n">
-        <v>0.047067</v>
+        <v>0.019216</v>
       </c>
     </row>
     <row r="219">
       <c r="A219" t="inlineStr">
         <is>
-          <t>ENSMUSG00000033715</t>
+          <t>ENSMUSG00000031765</t>
         </is>
       </c>
       <c r="B219" t="inlineStr">
         <is>
-          <t>Akr1c14</t>
+          <t>Mt1</t>
         </is>
       </c>
       <c r="C219" t="n">
-        <v>-0.7353</v>
+        <v>3.4398</v>
       </c>
       <c r="D219" t="n">
-        <v>0.037176</v>
+        <v>0</v>
       </c>
     </row>
     <row r="220">
       <c r="A220" t="inlineStr">
         <is>
-          <t>ENSMUSG00000033831</t>
+          <t>ENSMUSG00000031762</t>
         </is>
       </c>
       <c r="B220" t="inlineStr">
         <is>
-          <t>Fgb</t>
+          <t>Mt2</t>
         </is>
       </c>
       <c r="C220" t="n">
-        <v>0.9001</v>
+        <v>3.7775</v>
       </c>
       <c r="D220" t="n">
-        <v>0.004241</v>
+        <v>1.6e-05</v>
       </c>
     </row>
     <row r="221">
       <c r="A221" t="inlineStr">
         <is>
-          <t>ENSMUSG00000033860</t>
+          <t>ENSMUSG00000041241</t>
         </is>
       </c>
       <c r="B221" t="inlineStr">
         <is>
-          <t>Fgg</t>
+          <t>Mul1</t>
         </is>
       </c>
       <c r="C221" t="n">
-        <v>0.8889</v>
+        <v>0.6535</v>
       </c>
       <c r="D221" t="n">
-        <v>0.003052</v>
+        <v>0.04543</v>
       </c>
     </row>
     <row r="222">
       <c r="A222" t="inlineStr">
         <is>
-          <t>ENSMUSG00000034158</t>
+          <t>ENSMUSG00000078672</t>
         </is>
       </c>
       <c r="B222" t="inlineStr">
         <is>
-          <t>Lrrc58</t>
+          <t>Mup20</t>
         </is>
       </c>
       <c r="C222" t="n">
-        <v>-0.6676</v>
+        <v>-1.7554</v>
       </c>
       <c r="D222" t="n">
-        <v>0.000842</v>
+        <v>1e-06</v>
       </c>
     </row>
     <row r="223">
       <c r="A223" t="inlineStr">
         <is>
-          <t>ENSMUSG00000034258</t>
+          <t>ENSMUSG00000066154</t>
         </is>
       </c>
       <c r="B223" t="inlineStr">
         <is>
-          <t>Flvcr2</t>
+          <t>Mup3</t>
         </is>
       </c>
       <c r="C223" t="n">
-        <v>1.6538</v>
+        <v>-0.9781</v>
       </c>
       <c r="D223" t="n">
-        <v>0.043688</v>
+        <v>0.044533</v>
       </c>
     </row>
     <row r="224">
       <c r="A224" t="inlineStr">
         <is>
-          <t>ENSMUSG00000034353</t>
+          <t>ENSMUSG00000068566</t>
         </is>
       </c>
       <c r="B224" t="inlineStr">
         <is>
-          <t>Ramp1</t>
+          <t>Myadm</t>
         </is>
       </c>
       <c r="C224" t="n">
-        <v>1.0502</v>
+        <v>0.8206</v>
       </c>
       <c r="D224" t="n">
-        <v>0.012009</v>
+        <v>0.024819</v>
       </c>
     </row>
     <row r="225">
       <c r="A225" t="inlineStr">
         <is>
-          <t>ENSMUSG00000034371</t>
+          <t>ENSMUSG00000022346</t>
         </is>
       </c>
       <c r="B225" t="inlineStr">
         <is>
-          <t>Tkfc</t>
+          <t>Myc</t>
         </is>
       </c>
       <c r="C225" t="n">
-        <v>-0.6889999999999999</v>
+        <v>-3.1808</v>
       </c>
       <c r="D225" t="n">
-        <v>7.8e-05</v>
+        <v>0.012009</v>
       </c>
     </row>
     <row r="226">
       <c r="A226" t="inlineStr">
         <is>
-          <t>ENSMUSG00000034591</t>
+          <t>ENSMUSG00000027201</t>
         </is>
       </c>
       <c r="B226" t="inlineStr">
         <is>
-          <t>Slc41a2</t>
+          <t>Myef2</t>
         </is>
       </c>
       <c r="C226" t="n">
-        <v>1.5706</v>
+        <v>-2.0042</v>
       </c>
       <c r="D226" t="n">
-        <v>0.025456</v>
+        <v>0.049479</v>
       </c>
     </row>
     <row r="227">
       <c r="A227" t="inlineStr">
         <is>
-          <t>ENSMUSG00000034723</t>
+          <t>ENSMUSG00000030004</t>
         </is>
       </c>
       <c r="B227" t="inlineStr">
         <is>
-          <t>Tmx4</t>
+          <t>Nat8</t>
         </is>
       </c>
       <c r="C227" t="n">
-        <v>-1.6054</v>
+        <v>1.3492</v>
       </c>
       <c r="D227" t="n">
-        <v>0.041204</v>
+        <v>1.1e-05</v>
       </c>
     </row>
     <row r="228">
       <c r="A228" t="inlineStr">
         <is>
-          <t>ENSMUSG00000034774</t>
+          <t>ENSMUSG00000033634</t>
         </is>
       </c>
       <c r="B228" t="inlineStr">
         <is>
-          <t>Dsg1c</t>
+          <t>Nat8f2</t>
         </is>
       </c>
       <c r="C228" t="n">
-        <v>3.1588</v>
+        <v>0.8129</v>
       </c>
       <c r="D228" t="n">
-        <v>0</v>
+        <v>0.003702</v>
       </c>
     </row>
     <row r="229">
       <c r="A229" t="inlineStr">
         <is>
-          <t>ENSMUSG00000034837</t>
+          <t>ENSMUSG00000068299</t>
         </is>
       </c>
       <c r="B229" t="inlineStr">
         <is>
-          <t>Gnat1</t>
+          <t>Nat8f4</t>
         </is>
       </c>
       <c r="C229" t="n">
-        <v>1.1984</v>
+        <v>1.0956</v>
       </c>
       <c r="D229" t="n">
-        <v>0.003422</v>
+        <v>0.011935</v>
       </c>
     </row>
     <row r="230">
       <c r="A230" t="inlineStr">
         <is>
-          <t>ENSMUSG00000034926</t>
+          <t>ENSMUSG00000089694</t>
         </is>
       </c>
       <c r="B230" t="inlineStr">
         <is>
-          <t>Dhcr24</t>
+          <t>Nat8f7</t>
         </is>
       </c>
       <c r="C230" t="n">
-        <v>0.5749</v>
+        <v>4.3763</v>
       </c>
       <c r="D230" t="n">
-        <v>0.032929</v>
+        <v>0.021096</v>
       </c>
     </row>
     <row r="231">
       <c r="A231" t="inlineStr">
         <is>
-          <t>ENSMUSG00000035356</t>
+          <t>ENSMUSG00000071715</t>
         </is>
       </c>
       <c r="B231" t="inlineStr">
         <is>
-          <t>Nfkbiz</t>
+          <t>Ncf4</t>
         </is>
       </c>
       <c r="C231" t="n">
-        <v>1.4335</v>
+        <v>1.5477</v>
       </c>
       <c r="D231" t="n">
-        <v>0.009748</v>
+        <v>0.006235</v>
       </c>
     </row>
     <row r="232">
       <c r="A232" t="inlineStr">
         <is>
-          <t>ENSMUSG00000035493</t>
+          <t>ENSMUSG00000037916</t>
         </is>
       </c>
       <c r="B232" t="inlineStr">
         <is>
-          <t>Tgfbi</t>
+          <t>Ndufv1</t>
         </is>
       </c>
       <c r="C232" t="n">
-        <v>0.6888</v>
+        <v>-0.5272</v>
       </c>
       <c r="D232" t="n">
-        <v>0.037339</v>
+        <v>0.025471</v>
       </c>
     </row>
     <row r="233">
       <c r="A233" t="inlineStr">
         <is>
-          <t>ENSMUSG00000035621</t>
+          <t>ENSMUSG00000092274</t>
         </is>
       </c>
       <c r="B233" t="inlineStr">
         <is>
-          <t>Midn</t>
+          <t>Neat1</t>
         </is>
       </c>
       <c r="C233" t="n">
-        <v>0.8266</v>
+        <v>1.0489</v>
       </c>
       <c r="D233" t="n">
-        <v>0.004986</v>
+        <v>0.00572</v>
       </c>
     </row>
     <row r="234">
       <c r="A234" t="inlineStr">
         <is>
-          <t>ENSMUSG00000035811</t>
+          <t>ENSMUSG00000026393</t>
         </is>
       </c>
       <c r="B234" t="inlineStr">
         <is>
-          <t>Ugt2b35</t>
+          <t>Nek7</t>
         </is>
       </c>
       <c r="C234" t="n">
-        <v>-0.6855</v>
+        <v>-0.7504</v>
       </c>
       <c r="D234" t="n">
-        <v>0.01044</v>
+        <v>0.013163</v>
       </c>
     </row>
     <row r="235">
       <c r="A235" t="inlineStr">
         <is>
-          <t>ENSMUSG00000035836</t>
+          <t>ENSMUSG00000056749</t>
         </is>
       </c>
       <c r="B235" t="inlineStr">
         <is>
-          <t>Ugt2b1</t>
+          <t>Nfil3</t>
         </is>
       </c>
       <c r="C235" t="n">
-        <v>-1.2677</v>
+        <v>-0.8278</v>
       </c>
       <c r="D235" t="n">
-        <v>0.005529</v>
+        <v>0.001644</v>
       </c>
     </row>
     <row r="236">
       <c r="A236" t="inlineStr">
         <is>
-          <t>ENSMUSG00000036216</t>
+          <t>ENSMUSG00000035356</t>
         </is>
       </c>
       <c r="B236" t="inlineStr">
         <is>
-          <t>Leap2</t>
+          <t>Nfkbiz</t>
         </is>
       </c>
       <c r="C236" t="n">
-        <v>-0.5881999999999999</v>
+        <v>1.4335</v>
       </c>
       <c r="D236" t="n">
-        <v>0.012179</v>
+        <v>0.009748</v>
       </c>
     </row>
     <row r="237">
       <c r="A237" t="inlineStr">
         <is>
-          <t>ENSMUSG00000036402</t>
+          <t>ENSMUSG00000016409</t>
         </is>
       </c>
       <c r="B237" t="inlineStr">
         <is>
-          <t>Gng12</t>
+          <t>Nkap</t>
         </is>
       </c>
       <c r="C237" t="n">
-        <v>-0.6671</v>
+        <v>-1.1426</v>
       </c>
       <c r="D237" t="n">
-        <v>0.012009</v>
+        <v>0.013688</v>
       </c>
     </row>
     <row r="238">
       <c r="A238" t="inlineStr">
         <is>
-          <t>ENSMUSG00000036752</t>
+          <t>ENSMUSG00000026643</t>
         </is>
       </c>
       <c r="B238" t="inlineStr">
         <is>
-          <t>Tubb4b</t>
+          <t>Nmt2</t>
         </is>
       </c>
       <c r="C238" t="n">
-        <v>-0.6359</v>
+        <v>-0.779</v>
       </c>
       <c r="D238" t="n">
-        <v>0.024564</v>
+        <v>0.000727</v>
       </c>
     </row>
     <row r="239">
       <c r="A239" t="inlineStr">
         <is>
-          <t>ENSMUSG00000036764</t>
+          <t>ENSMUSG00000021392</t>
         </is>
       </c>
       <c r="B239" t="inlineStr">
         <is>
-          <t>Dnajc12</t>
+          <t>Nol8</t>
         </is>
       </c>
       <c r="C239" t="n">
-        <v>1.6567</v>
+        <v>-1.4926</v>
       </c>
       <c r="D239" t="n">
-        <v>0.034793</v>
+        <v>0.046254</v>
       </c>
     </row>
     <row r="240">
       <c r="A240" t="inlineStr">
         <is>
-          <t>ENSMUSG00000037095</t>
+          <t>ENSMUSG00000027378</t>
         </is>
       </c>
       <c r="B240" t="inlineStr">
         <is>
-          <t>Lrg1</t>
+          <t>Nphp1</t>
         </is>
       </c>
       <c r="C240" t="n">
-        <v>1.6572</v>
+        <v>1.4616</v>
       </c>
       <c r="D240" t="n">
-        <v>0.000301</v>
+        <v>0.030415</v>
       </c>
     </row>
     <row r="241">
       <c r="A241" t="inlineStr">
         <is>
-          <t>ENSMUSG00000037166</t>
+          <t>ENSMUSG00000020889</t>
         </is>
       </c>
       <c r="B241" t="inlineStr">
         <is>
-          <t>Ppp1r14a</t>
+          <t>Nr1d1</t>
         </is>
       </c>
       <c r="C241" t="n">
-        <v>1.4691</v>
+        <v>2.7088</v>
       </c>
       <c r="D241" t="n">
-        <v>0.048323</v>
+        <v>0</v>
       </c>
     </row>
     <row r="242">
       <c r="A242" t="inlineStr">
         <is>
-          <t>ENSMUSG00000037722</t>
+          <t>ENSMUSG00000021775</t>
         </is>
       </c>
       <c r="B242" t="inlineStr">
         <is>
-          <t>Gnpnat1</t>
+          <t>Nr1d2</t>
         </is>
       </c>
       <c r="C242" t="n">
-        <v>-1.5099</v>
+        <v>2.3108</v>
       </c>
       <c r="D242" t="n">
-        <v>0.001961</v>
+        <v>0.001548</v>
       </c>
     </row>
     <row r="243">
       <c r="A243" t="inlineStr">
         <is>
-          <t>ENSMUSG00000037798</t>
+          <t>ENSMUSG00000024431</t>
         </is>
       </c>
       <c r="B243" t="inlineStr">
         <is>
-          <t>Mat1a</t>
+          <t>Nr3c1</t>
         </is>
       </c>
       <c r="C243" t="n">
-        <v>0.6911</v>
+        <v>-1.4757</v>
       </c>
       <c r="D243" t="n">
-        <v>0.034907</v>
+        <v>0</v>
       </c>
     </row>
     <row r="244">
       <c r="A244" t="inlineStr">
         <is>
-          <t>ENSMUSG00000037916</t>
+          <t>ENSMUSG00000049107</t>
         </is>
       </c>
       <c r="B244" t="inlineStr">
         <is>
-          <t>Ndufv1</t>
+          <t>Ntf3</t>
         </is>
       </c>
       <c r="C244" t="n">
-        <v>-0.5272</v>
+        <v>3.2728</v>
       </c>
       <c r="D244" t="n">
-        <v>0.025471</v>
+        <v>0.001788</v>
       </c>
     </row>
     <row r="245">
       <c r="A245" t="inlineStr">
         <is>
-          <t>ENSMUSG00000038155</t>
+          <t>ENSMUSG00000026999</t>
         </is>
       </c>
       <c r="B245" t="inlineStr">
         <is>
-          <t>Gstp2</t>
+          <t>Nup35</t>
         </is>
       </c>
       <c r="C245" t="n">
-        <v>-6.0092</v>
+        <v>-2.5196</v>
       </c>
       <c r="D245" t="n">
-        <v>0.017515</v>
+        <v>0.040087</v>
       </c>
     </row>
     <row r="246">
       <c r="A246" t="inlineStr">
         <is>
-          <t>ENSMUSG00000038224</t>
+          <t>ENSMUSG00000061540</t>
         </is>
       </c>
       <c r="B246" t="inlineStr">
         <is>
-          <t>Serpinf2</t>
+          <t>Orm2</t>
         </is>
       </c>
       <c r="C246" t="n">
-        <v>1.0429</v>
+        <v>8.6198</v>
       </c>
       <c r="D246" t="n">
         <v>1e-06</v>
@@ -4863,1456 +4863,1456 @@
     <row r="247">
       <c r="A247" t="inlineStr">
         <is>
-          <t>ENSMUSG00000038357</t>
+          <t>ENSMUSG00000028359</t>
         </is>
       </c>
       <c r="B247" t="inlineStr">
         <is>
-          <t>Camp</t>
+          <t>Orm3</t>
         </is>
       </c>
       <c r="C247" t="n">
-        <v>6.4288</v>
+        <v>4.2992</v>
       </c>
       <c r="D247" t="n">
-        <v>0.002789</v>
+        <v>0</v>
       </c>
     </row>
     <row r="248">
       <c r="A248" t="inlineStr">
         <is>
-          <t>ENSMUSG00000038418</t>
+          <t>ENSMUSG00000019916</t>
         </is>
       </c>
       <c r="B248" t="inlineStr">
         <is>
-          <t>Egr1</t>
+          <t>P4ha1</t>
         </is>
       </c>
       <c r="C248" t="n">
-        <v>3.191</v>
+        <v>-0.844</v>
       </c>
       <c r="D248" t="n">
-        <v>0.039949</v>
+        <v>0.029268</v>
       </c>
     </row>
     <row r="249">
       <c r="A249" t="inlineStr">
         <is>
-          <t>ENSMUSG00000038508</t>
+          <t>ENSMUSG00000078931</t>
         </is>
       </c>
       <c r="B249" t="inlineStr">
         <is>
-          <t>Gdf15</t>
+          <t>Pdf</t>
         </is>
       </c>
       <c r="C249" t="n">
-        <v>0.9167999999999999</v>
+        <v>-6.0704</v>
       </c>
       <c r="D249" t="n">
-        <v>0.021382</v>
+        <v>0.009920999999999999</v>
       </c>
     </row>
     <row r="250">
       <c r="A250" t="inlineStr">
         <is>
-          <t>ENSMUSG00000038550</t>
+          <t>ENSMUSG00000002265</t>
         </is>
       </c>
       <c r="B250" t="inlineStr">
         <is>
-          <t>Ciart</t>
+          <t>Peg3</t>
         </is>
       </c>
       <c r="C250" t="n">
-        <v>2.2746</v>
+        <v>-2.0382</v>
       </c>
       <c r="D250" t="n">
-        <v>9.6e-05</v>
+        <v>0.026829</v>
       </c>
     </row>
     <row r="251">
       <c r="A251" t="inlineStr">
         <is>
-          <t>ENSMUSG00000038776</t>
+          <t>ENSMUSG00000028957</t>
         </is>
       </c>
       <c r="B251" t="inlineStr">
         <is>
-          <t>Ephx1</t>
+          <t>Per3</t>
         </is>
       </c>
       <c r="C251" t="n">
-        <v>-0.9754</v>
+        <v>2.0869</v>
       </c>
       <c r="D251" t="n">
-        <v>0.005529</v>
+        <v>5e-06</v>
       </c>
     </row>
     <row r="252">
       <c r="A252" t="inlineStr">
         <is>
-          <t>ENSMUSG00000038894</t>
+          <t>ENSMUSG00000043445</t>
         </is>
       </c>
       <c r="B252" t="inlineStr">
         <is>
-          <t>Irs2</t>
+          <t>Pgp</t>
         </is>
       </c>
       <c r="C252" t="n">
-        <v>-1.1475</v>
+        <v>-0.5678</v>
       </c>
       <c r="D252" t="n">
-        <v>2.8e-05</v>
+        <v>0.044533</v>
       </c>
     </row>
     <row r="253">
       <c r="A253" t="inlineStr">
         <is>
-          <t>ENSMUSG00000039168</t>
+          <t>ENSMUSG00000044340</t>
         </is>
       </c>
       <c r="B253" t="inlineStr">
         <is>
-          <t>Dap</t>
+          <t>Phlpp1</t>
         </is>
       </c>
       <c r="C253" t="n">
-        <v>0.5135999999999999</v>
+        <v>-1.6521</v>
       </c>
       <c r="D253" t="n">
-        <v>0.005069</v>
+        <v>0.013777</v>
       </c>
     </row>
     <row r="254">
       <c r="A254" t="inlineStr">
         <is>
-          <t>ENSMUSG00000039533</t>
+          <t>ENSMUSG00000029186</t>
         </is>
       </c>
       <c r="B254" t="inlineStr">
         <is>
-          <t>Mmd2</t>
+          <t>Pi4k2b</t>
         </is>
       </c>
       <c r="C254" t="n">
-        <v>3.2568</v>
+        <v>-0.7049</v>
       </c>
       <c r="D254" t="n">
-        <v>3.9e-05</v>
+        <v>0.023389</v>
       </c>
     </row>
     <row r="255">
       <c r="A255" t="inlineStr">
         <is>
-          <t>ENSMUSG00000039616</t>
+          <t>ENSMUSG00000025017</t>
         </is>
       </c>
       <c r="B255" t="inlineStr">
         <is>
-          <t>Mocos</t>
+          <t>Pik3ap1</t>
         </is>
       </c>
       <c r="C255" t="n">
-        <v>-0.6057</v>
+        <v>0.8877</v>
       </c>
       <c r="D255" t="n">
-        <v>0.047959</v>
+        <v>0.002789</v>
       </c>
     </row>
     <row r="256">
       <c r="A256" t="inlineStr">
         <is>
-          <t>ENSMUSG00000039682</t>
+          <t>ENSMUSG00000058818</t>
         </is>
       </c>
       <c r="B256" t="inlineStr">
         <is>
-          <t>Lap3</t>
+          <t>Pirb</t>
         </is>
       </c>
       <c r="C256" t="n">
-        <v>-2.6446</v>
+        <v>1.0261</v>
       </c>
       <c r="D256" t="n">
-        <v>0.027911</v>
+        <v>0.036496</v>
       </c>
     </row>
     <row r="257">
       <c r="A257" t="inlineStr">
         <is>
-          <t>ENSMUSG00000039745</t>
+          <t>ENSMUSG00000041237</t>
         </is>
       </c>
       <c r="B257" t="inlineStr">
         <is>
-          <t>Htatip2</t>
+          <t>Pklr</t>
         </is>
       </c>
       <c r="C257" t="n">
-        <v>-0.7983</v>
+        <v>-1.5812</v>
       </c>
       <c r="D257" t="n">
-        <v>0.002988</v>
+        <v>1e-06</v>
       </c>
     </row>
     <row r="258">
       <c r="A258" t="inlineStr">
         <is>
-          <t>ENSMUSG00000039910</t>
+          <t>ENSMUSG00000059481</t>
         </is>
       </c>
       <c r="B258" t="inlineStr">
         <is>
-          <t>Cited2</t>
+          <t>Plg</t>
         </is>
       </c>
       <c r="C258" t="n">
-        <v>-0.661</v>
+        <v>0.551</v>
       </c>
       <c r="D258" t="n">
-        <v>0.044836</v>
+        <v>0.000593</v>
       </c>
     </row>
     <row r="259">
       <c r="A259" t="inlineStr">
         <is>
-          <t>ENSMUSG00000039958</t>
+          <t>ENSMUSG00000028494</t>
         </is>
       </c>
       <c r="B259" t="inlineStr">
         <is>
-          <t>Etfbkmt</t>
+          <t>Plin2</t>
         </is>
       </c>
       <c r="C259" t="n">
-        <v>-0.781</v>
+        <v>0.6223</v>
       </c>
       <c r="D259" t="n">
-        <v>0.008577</v>
+        <v>0.026379</v>
       </c>
     </row>
     <row r="260">
       <c r="A260" t="inlineStr">
         <is>
-          <t>ENSMUSG00000040017</t>
+          <t>ENSMUSG00000019461</t>
         </is>
       </c>
       <c r="B260" t="inlineStr">
         <is>
-          <t>Saa4</t>
+          <t>Plscr3</t>
         </is>
       </c>
       <c r="C260" t="n">
-        <v>1.4812</v>
+        <v>1.1052</v>
       </c>
       <c r="D260" t="n">
-        <v>0.000498</v>
+        <v>0.007732</v>
       </c>
     </row>
     <row r="261">
       <c r="A261" t="inlineStr">
         <is>
-          <t>ENSMUSG00000040127</t>
+          <t>ENSMUSG00000026179</t>
         </is>
       </c>
       <c r="B261" t="inlineStr">
         <is>
-          <t>Sdr9c7</t>
+          <t>Pnkd</t>
         </is>
       </c>
       <c r="C261" t="n">
-        <v>-1.3913</v>
+        <v>-0.5076000000000001</v>
       </c>
       <c r="D261" t="n">
-        <v>0.02793</v>
+        <v>0.028914</v>
       </c>
     </row>
     <row r="262">
       <c r="A262" t="inlineStr">
         <is>
-          <t>ENSMUSG00000040269</t>
+          <t>ENSMUSG00000115338</t>
         </is>
       </c>
       <c r="B262" t="inlineStr">
         <is>
-          <t>Mrps28</t>
+          <t>Pnp</t>
         </is>
       </c>
       <c r="C262" t="n">
-        <v>-1.4618</v>
+        <v>-0.6788999999999999</v>
       </c>
       <c r="D262" t="n">
-        <v>0.019216</v>
+        <v>0.025569</v>
       </c>
     </row>
     <row r="263">
       <c r="A263" t="inlineStr">
         <is>
-          <t>ENSMUSG00000040464</t>
+          <t>ENSMUSG00000005514</t>
         </is>
       </c>
       <c r="B263" t="inlineStr">
         <is>
-          <t>Gtpbp10</t>
+          <t>Por</t>
         </is>
       </c>
       <c r="C263" t="n">
-        <v>-2.2538</v>
+        <v>0.7701</v>
       </c>
       <c r="D263" t="n">
-        <v>0.00043</v>
+        <v>0.00436</v>
       </c>
     </row>
     <row r="264">
       <c r="A264" t="inlineStr">
         <is>
-          <t>ENSMUSG00000040562</t>
+          <t>ENSMUSG00000037166</t>
         </is>
       </c>
       <c r="B264" t="inlineStr">
         <is>
-          <t>Gstm2</t>
+          <t>Ppp1r14a</t>
         </is>
       </c>
       <c r="C264" t="n">
-        <v>-0.9704</v>
+        <v>1.4691</v>
       </c>
       <c r="D264" t="n">
-        <v>0.026829</v>
+        <v>0.048323</v>
       </c>
     </row>
     <row r="265">
       <c r="A265" t="inlineStr">
         <is>
-          <t>ENSMUSG00000040612</t>
+          <t>ENSMUSG00000022092</t>
         </is>
       </c>
       <c r="B265" t="inlineStr">
         <is>
-          <t>Ildr2</t>
+          <t>Ppp3cc</t>
         </is>
       </c>
       <c r="C265" t="n">
-        <v>0.9314</v>
+        <v>1.5896</v>
       </c>
       <c r="D265" t="n">
-        <v>0.004242</v>
+        <v>0.00106</v>
       </c>
     </row>
     <row r="266">
       <c r="A266" t="inlineStr">
         <is>
-          <t>ENSMUSG00000040660</t>
+          <t>ENSMUSG00000024127</t>
         </is>
       </c>
       <c r="B266" t="inlineStr">
         <is>
-          <t>Cyp2b9</t>
+          <t>Prepl</t>
         </is>
       </c>
       <c r="C266" t="n">
-        <v>5.7992</v>
+        <v>0.945</v>
       </c>
       <c r="D266" t="n">
-        <v>0</v>
+        <v>0.034235</v>
       </c>
     </row>
     <row r="267">
       <c r="A267" t="inlineStr">
         <is>
-          <t>ENSMUSG00000040746</t>
+          <t>ENSMUSG00000006014</t>
         </is>
       </c>
       <c r="B267" t="inlineStr">
         <is>
-          <t>Rnf167</t>
+          <t>Prg4</t>
         </is>
       </c>
       <c r="C267" t="n">
-        <v>1.5196</v>
+        <v>1.2553</v>
       </c>
       <c r="D267" t="n">
-        <v>0</v>
+        <v>0.005212</v>
       </c>
     </row>
     <row r="268">
       <c r="A268" t="inlineStr">
         <is>
-          <t>ENSMUSG00000040857</t>
+          <t>ENSMUSG00000026778</t>
         </is>
       </c>
       <c r="B268" t="inlineStr">
         <is>
-          <t>Erf</t>
+          <t>Prkcq</t>
         </is>
       </c>
       <c r="C268" t="n">
-        <v>0.6855</v>
+        <v>2.507</v>
       </c>
       <c r="D268" t="n">
-        <v>0.018549</v>
+        <v>0.025456</v>
       </c>
     </row>
     <row r="269">
       <c r="A269" t="inlineStr">
         <is>
-          <t>ENSMUSG00000040964</t>
+          <t>ENSMUSG00000005268</t>
         </is>
       </c>
       <c r="B269" t="inlineStr">
         <is>
-          <t>Arhgef10l</t>
+          <t>Prlr</t>
         </is>
       </c>
       <c r="C269" t="n">
-        <v>0.8807</v>
+        <v>0.9199000000000001</v>
       </c>
       <c r="D269" t="n">
-        <v>0.038152</v>
+        <v>0.043947</v>
       </c>
     </row>
     <row r="270">
       <c r="A270" t="inlineStr">
         <is>
-          <t>ENSMUSG00000041237</t>
+          <t>ENSMUSG00000057729</t>
         </is>
       </c>
       <c r="B270" t="inlineStr">
         <is>
-          <t>Pklr</t>
+          <t>Prtn3</t>
         </is>
       </c>
       <c r="C270" t="n">
-        <v>-1.5812</v>
+        <v>5.7007</v>
       </c>
       <c r="D270" t="n">
-        <v>1e-06</v>
+        <v>1e-05</v>
       </c>
     </row>
     <row r="271">
       <c r="A271" t="inlineStr">
         <is>
-          <t>ENSMUSG00000041241</t>
+          <t>ENSMUSG00000031897</t>
         </is>
       </c>
       <c r="B271" t="inlineStr">
         <is>
-          <t>Mul1</t>
+          <t>Psmb10</t>
         </is>
       </c>
       <c r="C271" t="n">
-        <v>0.6535</v>
+        <v>0.5258</v>
       </c>
       <c r="D271" t="n">
-        <v>0.04543</v>
+        <v>0.02535</v>
       </c>
     </row>
     <row r="272">
       <c r="A272" t="inlineStr">
         <is>
-          <t>ENSMUSG00000041930</t>
+          <t>ENSMUSG00000033684</t>
         </is>
       </c>
       <c r="B272" t="inlineStr">
         <is>
-          <t>Fam222a</t>
+          <t>Qsox1</t>
         </is>
       </c>
       <c r="C272" t="n">
-        <v>-1.4331</v>
+        <v>0.6951000000000001</v>
       </c>
       <c r="D272" t="n">
-        <v>0.000712</v>
+        <v>0.047067</v>
       </c>
     </row>
     <row r="273">
       <c r="A273" t="inlineStr">
         <is>
-          <t>ENSMUSG00000042305</t>
+          <t>ENSMUSG00000059060</t>
         </is>
       </c>
       <c r="B273" t="inlineStr">
         <is>
-          <t>Tmem183a</t>
+          <t>Rad51b</t>
         </is>
       </c>
       <c r="C273" t="n">
-        <v>-1.1959</v>
+        <v>1.5592</v>
       </c>
       <c r="D273" t="n">
-        <v>0.008946000000000001</v>
+        <v>0.043202</v>
       </c>
     </row>
     <row r="274">
       <c r="A274" t="inlineStr">
         <is>
-          <t>ENSMUSG00000043445</t>
+          <t>ENSMUSG00000034353</t>
         </is>
       </c>
       <c r="B274" t="inlineStr">
         <is>
-          <t>Pgp</t>
+          <t>Ramp1</t>
         </is>
       </c>
       <c r="C274" t="n">
-        <v>-0.5678</v>
+        <v>1.0502</v>
       </c>
       <c r="D274" t="n">
-        <v>0.044533</v>
+        <v>0.012009</v>
       </c>
     </row>
     <row r="275">
       <c r="A275" t="inlineStr">
         <is>
-          <t>ENSMUSG00000044066</t>
+          <t>ENSMUSG00000046402</t>
         </is>
       </c>
       <c r="B275" t="inlineStr">
         <is>
-          <t>Cep68</t>
+          <t>Rbp1</t>
         </is>
       </c>
       <c r="C275" t="n">
-        <v>-1.0223</v>
+        <v>1.6151</v>
       </c>
       <c r="D275" t="n">
-        <v>0.036795</v>
+        <v>0</v>
       </c>
     </row>
     <row r="276">
       <c r="A276" t="inlineStr">
         <is>
-          <t>ENSMUSG00000044068</t>
+          <t>ENSMUSG00000024785</t>
         </is>
       </c>
       <c r="B276" t="inlineStr">
         <is>
-          <t>Zrsr1</t>
+          <t>Rcl1</t>
         </is>
       </c>
       <c r="C276" t="n">
-        <v>-0.9405</v>
+        <v>0.8954</v>
       </c>
       <c r="D276" t="n">
-        <v>0.006308</v>
+        <v>0.001055</v>
       </c>
     </row>
     <row r="277">
       <c r="A277" t="inlineStr">
         <is>
-          <t>ENSMUSG00000044340</t>
+          <t>ENSMUSG00000074639</t>
         </is>
       </c>
       <c r="B277" t="inlineStr">
         <is>
-          <t>Phlpp1</t>
+          <t>Rdh16f2</t>
         </is>
       </c>
       <c r="C277" t="n">
-        <v>-1.6521</v>
+        <v>0.6189</v>
       </c>
       <c r="D277" t="n">
-        <v>0.013777</v>
+        <v>0.041586</v>
       </c>
     </row>
     <row r="278">
       <c r="A278" t="inlineStr">
         <is>
-          <t>ENSMUSG00000044349</t>
+          <t>ENSMUSG00000056148</t>
         </is>
       </c>
       <c r="B278" t="inlineStr">
         <is>
-          <t>Snhg11</t>
+          <t>Rdh9</t>
         </is>
       </c>
       <c r="C278" t="n">
-        <v>-3.6735</v>
+        <v>-1.4045</v>
       </c>
       <c r="D278" t="n">
-        <v>0.000112</v>
+        <v>8e-06</v>
       </c>
     </row>
     <row r="279">
       <c r="A279" t="inlineStr">
         <is>
-          <t>ENSMUSG00000044786</t>
+          <t>ENSMUSG00000070645</t>
         </is>
       </c>
       <c r="B279" t="inlineStr">
         <is>
-          <t>Zfp36</t>
+          <t>Ren1</t>
         </is>
       </c>
       <c r="C279" t="n">
-        <v>0.8459</v>
+        <v>8.276999999999999</v>
       </c>
       <c r="D279" t="n">
-        <v>0.000677</v>
+        <v>0</v>
       </c>
     </row>
     <row r="280">
       <c r="A280" t="inlineStr">
         <is>
-          <t>ENSMUSG00000044906</t>
+          <t>ENSMUSG00000021876</t>
         </is>
       </c>
       <c r="B280" t="inlineStr">
         <is>
-          <t>4930503L19Rik</t>
+          <t>Rnase4</t>
         </is>
       </c>
       <c r="C280" t="n">
-        <v>2.9642</v>
+        <v>0.8047</v>
       </c>
       <c r="D280" t="n">
-        <v>0.005953</v>
+        <v>0.007048</v>
       </c>
     </row>
     <row r="281">
       <c r="A281" t="inlineStr">
         <is>
-          <t>ENSMUSG00000045672</t>
+          <t>ENSMUSG00000033107</t>
         </is>
       </c>
       <c r="B281" t="inlineStr">
         <is>
-          <t>Col27a1</t>
+          <t>Rnf125</t>
         </is>
       </c>
       <c r="C281" t="n">
-        <v>-1.3706</v>
+        <v>-0.6397</v>
       </c>
       <c r="D281" t="n">
-        <v>0.000218</v>
+        <v>0.035107</v>
       </c>
     </row>
     <row r="282">
       <c r="A282" t="inlineStr">
         <is>
-          <t>ENSMUSG00000045775</t>
+          <t>ENSMUSG00000020642</t>
         </is>
       </c>
       <c r="B282" t="inlineStr">
         <is>
-          <t>Slc16a5</t>
+          <t>Rnf144a</t>
         </is>
       </c>
       <c r="C282" t="n">
-        <v>1.3157</v>
+        <v>-1.6495</v>
       </c>
       <c r="D282" t="n">
-        <v>0.017515</v>
+        <v>0.044533</v>
       </c>
     </row>
     <row r="283">
       <c r="A283" t="inlineStr">
         <is>
-          <t>ENSMUSG00000046352</t>
+          <t>ENSMUSG00000040746</t>
         </is>
       </c>
       <c r="B283" t="inlineStr">
         <is>
-          <t>Gjb2</t>
+          <t>Rnf167</t>
         </is>
       </c>
       <c r="C283" t="n">
-        <v>0.5836</v>
+        <v>1.5196</v>
       </c>
       <c r="D283" t="n">
-        <v>0.000471</v>
+        <v>0</v>
       </c>
     </row>
     <row r="284">
       <c r="A284" t="inlineStr">
         <is>
-          <t>ENSMUSG00000046402</t>
+          <t>ENSMUSG00000022540</t>
         </is>
       </c>
       <c r="B284" t="inlineStr">
         <is>
-          <t>Rbp1</t>
+          <t>Rogdi</t>
         </is>
       </c>
       <c r="C284" t="n">
-        <v>1.6151</v>
+        <v>1.29</v>
       </c>
       <c r="D284" t="n">
-        <v>0</v>
+        <v>6.2e-05</v>
       </c>
     </row>
     <row r="285">
       <c r="A285" t="inlineStr">
         <is>
-          <t>ENSMUSG00000046688</t>
+          <t>ENSMUSG00000028150</t>
         </is>
       </c>
       <c r="B285" t="inlineStr">
         <is>
-          <t>Tifa</t>
+          <t>Rorc</t>
         </is>
       </c>
       <c r="C285" t="n">
-        <v>2.3113</v>
+        <v>-0.7258</v>
       </c>
       <c r="D285" t="n">
-        <v>0.016857</v>
+        <v>0.022253</v>
       </c>
     </row>
     <row r="286">
       <c r="A286" t="inlineStr">
         <is>
-          <t>ENSMUSG00000048000</t>
+          <t>ENSMUSG00000003868</t>
         </is>
       </c>
       <c r="B286" t="inlineStr">
         <is>
-          <t>Gigyf2</t>
+          <t>Ruvbl2</t>
         </is>
       </c>
       <c r="C286" t="n">
-        <v>-0.9639</v>
+        <v>-2.053</v>
       </c>
       <c r="D286" t="n">
-        <v>0.002805</v>
+        <v>0.000677</v>
       </c>
     </row>
     <row r="287">
       <c r="A287" t="inlineStr">
         <is>
-          <t>ENSMUSG00000048154</t>
+          <t>ENSMUSG00000072872</t>
         </is>
       </c>
       <c r="B287" t="inlineStr">
         <is>
-          <t>Kmt2d</t>
+          <t>Rybp</t>
         </is>
       </c>
       <c r="C287" t="n">
-        <v>-2.1913</v>
+        <v>-2.4153</v>
       </c>
       <c r="D287" t="n">
-        <v>0.003023</v>
+        <v>0.012227</v>
       </c>
     </row>
     <row r="288">
       <c r="A288" t="inlineStr">
         <is>
-          <t>ENSMUSG00000048440</t>
+          <t>ENSMUSG00000056054</t>
         </is>
       </c>
       <c r="B288" t="inlineStr">
         <is>
-          <t>Cyp4f16</t>
+          <t>S100a8</t>
         </is>
       </c>
       <c r="C288" t="n">
-        <v>1.7204</v>
+        <v>4.1195</v>
       </c>
       <c r="D288" t="n">
-        <v>0.016931</v>
+        <v>0.000328</v>
       </c>
     </row>
     <row r="289">
       <c r="A289" t="inlineStr">
         <is>
-          <t>ENSMUSG00000048489</t>
+          <t>ENSMUSG00000056071</t>
         </is>
       </c>
       <c r="B289" t="inlineStr">
         <is>
-          <t>Depp1</t>
+          <t>S100a9</t>
         </is>
       </c>
       <c r="C289" t="n">
-        <v>0.9267</v>
+        <v>4.9938</v>
       </c>
       <c r="D289" t="n">
-        <v>0.002988</v>
+        <v>2.9e-05</v>
       </c>
     </row>
     <row r="290">
       <c r="A290" t="inlineStr">
         <is>
-          <t>ENSMUSG00000049107</t>
+          <t>ENSMUSG00000074115</t>
         </is>
       </c>
       <c r="B290" t="inlineStr">
         <is>
-          <t>Ntf3</t>
+          <t>Saa1</t>
         </is>
       </c>
       <c r="C290" t="n">
-        <v>3.2728</v>
+        <v>4.1014</v>
       </c>
       <c r="D290" t="n">
-        <v>0.001788</v>
+        <v>0.005165</v>
       </c>
     </row>
     <row r="291">
       <c r="A291" t="inlineStr">
         <is>
-          <t>ENSMUSG00000049382</t>
+          <t>ENSMUSG00000040017</t>
         </is>
       </c>
       <c r="B291" t="inlineStr">
         <is>
-          <t>Krt8</t>
+          <t>Saa4</t>
         </is>
       </c>
       <c r="C291" t="n">
-        <v>0.7038</v>
+        <v>1.4812</v>
       </c>
       <c r="D291" t="n">
-        <v>0.025989</v>
+        <v>0.000498</v>
       </c>
     </row>
     <row r="292">
       <c r="A292" t="inlineStr">
         <is>
-          <t>ENSMUSG00000049658</t>
+          <t>ENSMUSG00000022032</t>
         </is>
       </c>
       <c r="B292" t="inlineStr">
         <is>
-          <t>Bdp1</t>
+          <t>Scara5</t>
         </is>
       </c>
       <c r="C292" t="n">
-        <v>-1.9488</v>
+        <v>1.7102</v>
       </c>
       <c r="D292" t="n">
-        <v>0.019032</v>
+        <v>0.025569</v>
       </c>
     </row>
     <row r="293">
       <c r="A293" t="inlineStr">
         <is>
-          <t>ENSMUSG00000049988</t>
+          <t>ENSMUSG00000023033</t>
         </is>
       </c>
       <c r="B293" t="inlineStr">
         <is>
-          <t>Lrrc25</t>
+          <t>Scn8a</t>
         </is>
       </c>
       <c r="C293" t="n">
-        <v>1.18</v>
+        <v>2.7323</v>
       </c>
       <c r="D293" t="n">
-        <v>0.030934</v>
+        <v>0.000263</v>
       </c>
     </row>
     <row r="294">
       <c r="A294" t="inlineStr">
         <is>
-          <t>ENSMUSG00000051335</t>
+          <t>ENSMUSG00000025743</t>
         </is>
       </c>
       <c r="B294" t="inlineStr">
         <is>
-          <t>Gfod1</t>
+          <t>Sdc3</t>
         </is>
       </c>
       <c r="C294" t="n">
-        <v>-4.7222</v>
+        <v>1.3655</v>
       </c>
       <c r="D294" t="n">
-        <v>0.000883</v>
+        <v>0.004249</v>
       </c>
     </row>
     <row r="295">
       <c r="A295" t="inlineStr">
         <is>
-          <t>ENSMUSG00000051682</t>
+          <t>ENSMUSG00000040127</t>
         </is>
       </c>
       <c r="B295" t="inlineStr">
         <is>
-          <t>Treml4</t>
+          <t>Sdr9c7</t>
         </is>
       </c>
       <c r="C295" t="n">
-        <v>1.6583</v>
+        <v>-1.3913</v>
       </c>
       <c r="D295" t="n">
-        <v>0.032154</v>
+        <v>0.02793</v>
       </c>
     </row>
     <row r="296">
       <c r="A296" t="inlineStr">
         <is>
-          <t>ENSMUSG00000051748</t>
+          <t>ENSMUSG00000029597</t>
         </is>
       </c>
       <c r="B296" t="inlineStr">
         <is>
-          <t>Wfdc21</t>
+          <t>Sds</t>
         </is>
       </c>
       <c r="C296" t="n">
-        <v>0.7135</v>
+        <v>1.1685</v>
       </c>
       <c r="D296" t="n">
-        <v>0.012009</v>
+        <v>0.01044</v>
       </c>
     </row>
     <row r="297">
       <c r="A297" t="inlineStr">
         <is>
-          <t>ENSMUSG00000052726</t>
+          <t>ENSMUSG00000027706</t>
         </is>
       </c>
       <c r="B297" t="inlineStr">
         <is>
-          <t>Kcnt2</t>
+          <t>Sec62</t>
         </is>
       </c>
       <c r="C297" t="n">
-        <v>5.9137</v>
+        <v>-0.6302</v>
       </c>
       <c r="D297" t="n">
-        <v>0.00436</v>
+        <v>0.000709</v>
       </c>
     </row>
     <row r="298">
       <c r="A298" t="inlineStr">
         <is>
-          <t>ENSMUSG00000052837</t>
+          <t>ENSMUSG00000061947</t>
         </is>
       </c>
       <c r="B298" t="inlineStr">
         <is>
-          <t>Junb</t>
+          <t>Serpina10</t>
         </is>
       </c>
       <c r="C298" t="n">
-        <v>1.6567</v>
+        <v>1.0205</v>
       </c>
       <c r="D298" t="n">
-        <v>4.4e-05</v>
+        <v>0.011583</v>
       </c>
     </row>
     <row r="299">
       <c r="A299" t="inlineStr">
         <is>
-          <t>ENSMUSG00000053113</t>
+          <t>ENSMUSG00000021091</t>
         </is>
       </c>
       <c r="B299" t="inlineStr">
         <is>
-          <t>Socs3</t>
+          <t>Serpina3n</t>
         </is>
       </c>
       <c r="C299" t="n">
-        <v>1.4909</v>
+        <v>1.6712</v>
       </c>
       <c r="D299" t="n">
-        <v>0.038111</v>
+        <v>0.000428</v>
       </c>
     </row>
     <row r="300">
       <c r="A300" t="inlineStr">
         <is>
-          <t>ENSMUSG00000053560</t>
+          <t>ENSMUSG00000026315</t>
         </is>
       </c>
       <c r="B300" t="inlineStr">
         <is>
-          <t>Ier2</t>
+          <t>Serpinb8</t>
         </is>
       </c>
       <c r="C300" t="n">
-        <v>0.7547</v>
+        <v>1.6417</v>
       </c>
       <c r="D300" t="n">
-        <v>0.038152</v>
+        <v>0.017727</v>
       </c>
     </row>
     <row r="301">
       <c r="A301" t="inlineStr">
         <is>
-          <t>ENSMUSG00000053714</t>
+          <t>ENSMUSG00000026249</t>
         </is>
       </c>
       <c r="B301" t="inlineStr">
         <is>
-          <t>4732471J01Rik</t>
+          <t>Serpine2</t>
         </is>
       </c>
       <c r="C301" t="n">
-        <v>-3.7625</v>
+        <v>-2.6966</v>
       </c>
       <c r="D301" t="n">
-        <v>0.023211</v>
+        <v>0.000179</v>
       </c>
     </row>
     <row r="302">
       <c r="A302" t="inlineStr">
         <is>
-          <t>ENSMUSG00000053819</t>
+          <t>ENSMUSG00000038224</t>
         </is>
       </c>
       <c r="B302" t="inlineStr">
         <is>
-          <t>Camk2d</t>
+          <t>Serpinf2</t>
         </is>
       </c>
       <c r="C302" t="n">
-        <v>-3.3588</v>
+        <v>1.0429</v>
       </c>
       <c r="D302" t="n">
-        <v>0.003916</v>
+        <v>1e-06</v>
       </c>
     </row>
     <row r="303">
       <c r="A303" t="inlineStr">
         <is>
-          <t>ENSMUSG00000053907</t>
+          <t>ENSMUSG00000025036</t>
         </is>
       </c>
       <c r="B303" t="inlineStr">
         <is>
-          <t>Mat2a</t>
+          <t>Sfxn2</t>
         </is>
       </c>
       <c r="C303" t="n">
-        <v>0.7126</v>
+        <v>0.5276999999999999</v>
       </c>
       <c r="D303" t="n">
-        <v>0.001219</v>
+        <v>0.029363</v>
       </c>
     </row>
     <row r="304">
       <c r="A304" t="inlineStr">
         <is>
-          <t>ENSMUSG00000055116</t>
+          <t>ENSMUSG00000024976</t>
         </is>
       </c>
       <c r="B304" t="inlineStr">
         <is>
-          <t>Arntl</t>
+          <t>Shoc2</t>
         </is>
       </c>
       <c r="C304" t="n">
-        <v>-1.5653</v>
+        <v>-1.1441</v>
       </c>
       <c r="D304" t="n">
-        <v>0</v>
+        <v>0.04916</v>
       </c>
     </row>
     <row r="305">
       <c r="A305" t="inlineStr">
         <is>
-          <t>ENSMUSG00000055322</t>
+          <t>ENSMUSG00000020805</t>
         </is>
       </c>
       <c r="B305" t="inlineStr">
         <is>
-          <t>Tns1</t>
+          <t>Slc13a5</t>
         </is>
       </c>
       <c r="C305" t="n">
-        <v>-1.0308</v>
+        <v>6.4684</v>
       </c>
       <c r="D305" t="n">
-        <v>7.499999999999999e-05</v>
+        <v>0.000395</v>
       </c>
     </row>
     <row r="306">
       <c r="A306" t="inlineStr">
         <is>
-          <t>ENSMUSG00000055730</t>
+          <t>ENSMUSG00000045775</t>
         </is>
       </c>
       <c r="B306" t="inlineStr">
         <is>
-          <t>Ces2a</t>
+          <t>Slc16a5</t>
         </is>
       </c>
       <c r="C306" t="n">
-        <v>-1.0885</v>
+        <v>1.3157</v>
       </c>
       <c r="D306" t="n">
-        <v>0.001193</v>
+        <v>0.017515</v>
       </c>
     </row>
     <row r="307">
       <c r="A307" t="inlineStr">
         <is>
-          <t>ENSMUSG00000055884</t>
+          <t>ENSMUSG00000032449</t>
         </is>
       </c>
       <c r="B307" t="inlineStr">
         <is>
-          <t>Fancm</t>
+          <t>Slc25a36</t>
         </is>
       </c>
       <c r="C307" t="n">
-        <v>-3.0269</v>
+        <v>-3.3359</v>
       </c>
       <c r="D307" t="n">
-        <v>6.2e-05</v>
+        <v>0.042349</v>
       </c>
     </row>
     <row r="308">
       <c r="A308" t="inlineStr">
         <is>
-          <t>ENSMUSG00000056054</t>
+          <t>ENSMUSG00000010064</t>
         </is>
       </c>
       <c r="B308" t="inlineStr">
         <is>
-          <t>S100a8</t>
+          <t>Slc38a3</t>
         </is>
       </c>
       <c r="C308" t="n">
-        <v>4.1195</v>
+        <v>0.7902</v>
       </c>
       <c r="D308" t="n">
-        <v>0.000328</v>
+        <v>0</v>
       </c>
     </row>
     <row r="309">
       <c r="A309" t="inlineStr">
         <is>
-          <t>ENSMUSG00000056071</t>
+          <t>ENSMUSG00000022094</t>
         </is>
       </c>
       <c r="B309" t="inlineStr">
         <is>
-          <t>S100a9</t>
+          <t>Slc39a14</t>
         </is>
       </c>
       <c r="C309" t="n">
-        <v>4.9938</v>
+        <v>0.7171999999999999</v>
       </c>
       <c r="D309" t="n">
-        <v>2.9e-05</v>
+        <v>0.037622</v>
       </c>
     </row>
     <row r="310">
       <c r="A310" t="inlineStr">
         <is>
-          <t>ENSMUSG00000056148</t>
+          <t>ENSMUSG00000063354</t>
         </is>
       </c>
       <c r="B310" t="inlineStr">
         <is>
-          <t>Rdh9</t>
+          <t>Slc39a4</t>
         </is>
       </c>
       <c r="C310" t="n">
-        <v>-1.4045</v>
+        <v>-0.9926</v>
       </c>
       <c r="D310" t="n">
-        <v>8e-06</v>
+        <v>0.000147</v>
       </c>
     </row>
     <row r="311">
       <c r="A311" t="inlineStr">
         <is>
-          <t>ENSMUSG00000056268</t>
+          <t>ENSMUSG00000034591</t>
         </is>
       </c>
       <c r="B311" t="inlineStr">
         <is>
-          <t>Dennd1b</t>
+          <t>Slc41a2</t>
         </is>
       </c>
       <c r="C311" t="n">
-        <v>-2.5936</v>
+        <v>1.5706</v>
       </c>
       <c r="D311" t="n">
-        <v>0.017727</v>
+        <v>0.025456</v>
       </c>
     </row>
     <row r="312">
       <c r="A312" t="inlineStr">
         <is>
-          <t>ENSMUSG00000056501</t>
+          <t>ENSMUSG00000026435</t>
         </is>
       </c>
       <c r="B312" t="inlineStr">
         <is>
-          <t>Cebpb</t>
+          <t>Slc45a3</t>
         </is>
       </c>
       <c r="C312" t="n">
-        <v>0.6631</v>
+        <v>-0.7477</v>
       </c>
       <c r="D312" t="n">
-        <v>0.000647</v>
+        <v>0.035107</v>
       </c>
     </row>
     <row r="313">
       <c r="A313" t="inlineStr">
         <is>
-          <t>ENSMUSG00000056749</t>
+          <t>ENSMUSG00000028744</t>
         </is>
       </c>
       <c r="B313" t="inlineStr">
         <is>
-          <t>Nfil3</t>
+          <t>Slc66a1</t>
         </is>
       </c>
       <c r="C313" t="n">
-        <v>-0.8278</v>
+        <v>0.9434</v>
       </c>
       <c r="D313" t="n">
-        <v>0.001644</v>
+        <v>0.026718</v>
       </c>
     </row>
     <row r="314">
       <c r="A314" t="inlineStr">
         <is>
-          <t>ENSMUSG00000057074</t>
+          <t>ENSMUSG00000020733</t>
         </is>
       </c>
       <c r="B314" t="inlineStr">
         <is>
-          <t>Ces1g</t>
+          <t>Slc9a3r1</t>
         </is>
       </c>
       <c r="C314" t="n">
-        <v>0.6133999999999999</v>
+        <v>0.6091</v>
       </c>
       <c r="D314" t="n">
-        <v>0.000846</v>
+        <v>0.007624</v>
       </c>
     </row>
     <row r="315">
       <c r="A315" t="inlineStr">
         <is>
-          <t>ENSMUSG00000057315</t>
+          <t>ENSMUSG00000031715</t>
         </is>
       </c>
       <c r="B315" t="inlineStr">
         <is>
-          <t>Arhgap24</t>
+          <t>Smarca5</t>
         </is>
       </c>
       <c r="C315" t="n">
-        <v>-0.9619</v>
+        <v>-2.5062</v>
       </c>
       <c r="D315" t="n">
-        <v>0.044533</v>
+        <v>0.012227</v>
       </c>
     </row>
     <row r="316">
       <c r="A316" t="inlineStr">
         <is>
-          <t>ENSMUSG00000057342</t>
+          <t>ENSMUSG00000044349</t>
         </is>
       </c>
       <c r="B316" t="inlineStr">
         <is>
-          <t>Sphk2</t>
+          <t>Snhg11</t>
         </is>
       </c>
       <c r="C316" t="n">
-        <v>0.6757</v>
+        <v>-3.6735</v>
       </c>
       <c r="D316" t="n">
-        <v>0.000395</v>
+        <v>0.000112</v>
       </c>
     </row>
     <row r="317">
       <c r="A317" t="inlineStr">
         <is>
-          <t>ENSMUSG00000057729</t>
+          <t>ENSMUSG00000053113</t>
         </is>
       </c>
       <c r="B317" t="inlineStr">
         <is>
-          <t>Prtn3</t>
+          <t>Socs3</t>
         </is>
       </c>
       <c r="C317" t="n">
-        <v>5.7007</v>
+        <v>1.4909</v>
       </c>
       <c r="D317" t="n">
-        <v>1e-05</v>
+        <v>0.038111</v>
       </c>
     </row>
     <row r="318">
       <c r="A318" t="inlineStr">
         <is>
-          <t>ENSMUSG00000058135</t>
+          <t>ENSMUSG00000072941</t>
         </is>
       </c>
       <c r="B318" t="inlineStr">
         <is>
-          <t>Gstm1</t>
+          <t>Sod3</t>
         </is>
       </c>
       <c r="C318" t="n">
-        <v>-1.4177</v>
+        <v>0.5672</v>
       </c>
       <c r="D318" t="n">
-        <v>0</v>
+        <v>0.044801</v>
       </c>
     </row>
     <row r="319">
       <c r="A319" t="inlineStr">
         <is>
-          <t>ENSMUSG00000058672</t>
+          <t>ENSMUSG00000121349</t>
         </is>
       </c>
       <c r="B319" t="inlineStr">
         <is>
-          <t>Tubb2a</t>
+          <t>Speer6-ps1</t>
         </is>
       </c>
       <c r="C319" t="n">
-        <v>-1.2794</v>
+        <v>0.7079</v>
       </c>
       <c r="D319" t="n">
-        <v>0.00058</v>
+        <v>0.000683</v>
       </c>
     </row>
     <row r="320">
       <c r="A320" t="inlineStr">
         <is>
-          <t>ENSMUSG00000058818</t>
+          <t>ENSMUSG00000057342</t>
         </is>
       </c>
       <c r="B320" t="inlineStr">
         <is>
-          <t>Pirb</t>
+          <t>Sphk2</t>
         </is>
       </c>
       <c r="C320" t="n">
-        <v>1.0261</v>
+        <v>0.6757</v>
       </c>
       <c r="D320" t="n">
-        <v>0.036496</v>
+        <v>0.000395</v>
       </c>
     </row>
     <row r="321">
       <c r="A321" t="inlineStr">
         <is>
-          <t>ENSMUSG00000058952</t>
+          <t>ENSMUSG00000029304</t>
         </is>
       </c>
       <c r="B321" t="inlineStr">
         <is>
-          <t>Cfi</t>
+          <t>Spp1</t>
         </is>
       </c>
       <c r="C321" t="n">
-        <v>0.6591</v>
+        <v>1.267</v>
       </c>
       <c r="D321" t="n">
-        <v>0.00112</v>
+        <v>0.001788</v>
       </c>
     </row>
     <row r="322">
       <c r="A322" t="inlineStr">
         <is>
-          <t>ENSMUSG00000059060</t>
+          <t>ENSMUSG00000063919</t>
         </is>
       </c>
       <c r="B322" t="inlineStr">
         <is>
-          <t>Rad51b</t>
+          <t>Srrm4</t>
         </is>
       </c>
       <c r="C322" t="n">
-        <v>1.5592</v>
+        <v>2.8102</v>
       </c>
       <c r="D322" t="n">
-        <v>0.043202</v>
+        <v>0.000125</v>
       </c>
     </row>
     <row r="323">
       <c r="A323" t="inlineStr">
         <is>
-          <t>ENSMUSG00000059481</t>
+          <t>ENSMUSG00000071172</t>
         </is>
       </c>
       <c r="B323" t="inlineStr">
         <is>
-          <t>Plg</t>
+          <t>Srsf3</t>
         </is>
       </c>
       <c r="C323" t="n">
-        <v>0.551</v>
+        <v>0.871</v>
       </c>
       <c r="D323" t="n">
-        <v>0.000593</v>
+        <v>0.019236</v>
       </c>
     </row>
     <row r="324">
       <c r="A324" t="inlineStr">
         <is>
-          <t>ENSMUSG00000060034</t>
+          <t>ENSMUSG00000025862</t>
         </is>
       </c>
       <c r="B324" t="inlineStr">
         <is>
-          <t>Ctf2</t>
+          <t>Stag2</t>
         </is>
       </c>
       <c r="C324" t="n">
-        <v>-6.0188</v>
+        <v>-3.9005</v>
       </c>
       <c r="D324" t="n">
-        <v>0.0115</v>
+        <v>0.031489</v>
       </c>
     </row>
     <row r="325">
       <c r="A325" t="inlineStr">
         <is>
-          <t>ENSMUSG00000060459</t>
+          <t>ENSMUSG00000026277</t>
         </is>
       </c>
       <c r="B325" t="inlineStr">
         <is>
-          <t>Kng2</t>
+          <t>Stk25</t>
         </is>
       </c>
       <c r="C325" t="n">
-        <v>0.6615</v>
+        <v>-1.2442</v>
       </c>
       <c r="D325" t="n">
-        <v>0.000883</v>
+        <v>0.009344999999999999</v>
       </c>
     </row>
     <row r="326">
       <c r="A326" t="inlineStr">
         <is>
-          <t>ENSMUSG00000060803</t>
+          <t>ENSMUSG00000061455</t>
         </is>
       </c>
       <c r="B326" t="inlineStr">
         <is>
-          <t>Gstp1</t>
+          <t>Stx17</t>
         </is>
       </c>
       <c r="C326" t="n">
-        <v>-1.3267</v>
+        <v>-3.8692</v>
       </c>
       <c r="D326" t="n">
-        <v>0.002789</v>
+        <v>0</v>
       </c>
     </row>
     <row r="327">
       <c r="A327" t="inlineStr">
         <is>
-          <t>ENSMUSG00000061132</t>
+          <t>ENSMUSG00000019737</t>
         </is>
       </c>
       <c r="B327" t="inlineStr">
         <is>
-          <t>Blnk</t>
+          <t>Syne4</t>
         </is>
       </c>
       <c r="C327" t="n">
-        <v>3.1226</v>
+        <v>3.9237</v>
       </c>
       <c r="D327" t="n">
         <v>0</v>
@@ -6321,1333 +6321,1333 @@
     <row r="328">
       <c r="A328" t="inlineStr">
         <is>
-          <t>ENSMUSG00000061455</t>
+          <t>ENSMUSG00000031939</t>
         </is>
       </c>
       <c r="B328" t="inlineStr">
         <is>
-          <t>Stx17</t>
+          <t>Taf1d</t>
         </is>
       </c>
       <c r="C328" t="n">
-        <v>-3.8692</v>
+        <v>-0.8745000000000001</v>
       </c>
       <c r="D328" t="n">
-        <v>0</v>
+        <v>0.022153</v>
       </c>
     </row>
     <row r="329">
       <c r="A329" t="inlineStr">
         <is>
-          <t>ENSMUSG00000061540</t>
+          <t>ENSMUSG00000024118</t>
         </is>
       </c>
       <c r="B329" t="inlineStr">
         <is>
-          <t>Orm2</t>
+          <t>Tedc2</t>
         </is>
       </c>
       <c r="C329" t="n">
-        <v>8.6198</v>
+        <v>-0.5558999999999999</v>
       </c>
       <c r="D329" t="n">
-        <v>1e-06</v>
+        <v>0.012504</v>
       </c>
     </row>
     <row r="330">
       <c r="A330" t="inlineStr">
         <is>
-          <t>ENSMUSG00000061808</t>
+          <t>ENSMUSG00000022389</t>
         </is>
       </c>
       <c r="B330" t="inlineStr">
         <is>
-          <t>Ttr</t>
+          <t>Tef</t>
         </is>
       </c>
       <c r="C330" t="n">
-        <v>-0.7374000000000001</v>
+        <v>0.6037</v>
       </c>
       <c r="D330" t="n">
-        <v>3.7e-05</v>
+        <v>0.038152</v>
       </c>
     </row>
     <row r="331">
       <c r="A331" t="inlineStr">
         <is>
-          <t>ENSMUSG00000061825</t>
+          <t>ENSMUSG00000024029</t>
         </is>
       </c>
       <c r="B331" t="inlineStr">
         <is>
-          <t>Ces2c</t>
+          <t>Tff3</t>
         </is>
       </c>
       <c r="C331" t="n">
-        <v>-1.4872</v>
+        <v>4.8649</v>
       </c>
       <c r="D331" t="n">
-        <v>0.03964</v>
+        <v>0</v>
       </c>
     </row>
     <row r="332">
       <c r="A332" t="inlineStr">
         <is>
-          <t>ENSMUSG00000061947</t>
+          <t>ENSMUSG00000035493</t>
         </is>
       </c>
       <c r="B332" t="inlineStr">
         <is>
-          <t>Serpina10</t>
+          <t>Tgfbi</t>
         </is>
       </c>
       <c r="C332" t="n">
-        <v>1.0205</v>
+        <v>0.6888</v>
       </c>
       <c r="D332" t="n">
-        <v>0.011583</v>
+        <v>0.037339</v>
       </c>
     </row>
     <row r="333">
       <c r="A333" t="inlineStr">
         <is>
-          <t>ENSMUSG00000062580</t>
+          <t>ENSMUSG00000046688</t>
         </is>
       </c>
       <c r="B333" t="inlineStr">
         <is>
-          <t>Timm17a</t>
+          <t>Tifa</t>
         </is>
       </c>
       <c r="C333" t="n">
-        <v>-4.4787</v>
+        <v>2.3113</v>
       </c>
       <c r="D333" t="n">
-        <v>0</v>
+        <v>0.016857</v>
       </c>
     </row>
     <row r="334">
       <c r="A334" t="inlineStr">
         <is>
-          <t>ENSMUSG00000062825</t>
+          <t>ENSMUSG00000062580</t>
         </is>
       </c>
       <c r="B334" t="inlineStr">
         <is>
-          <t>Actg1</t>
+          <t>Timm17a</t>
         </is>
       </c>
       <c r="C334" t="n">
-        <v>0.8794</v>
+        <v>-4.4787</v>
       </c>
       <c r="D334" t="n">
-        <v>0.000848</v>
+        <v>0</v>
       </c>
     </row>
     <row r="335">
       <c r="A335" t="inlineStr">
         <is>
-          <t>ENSMUSG00000063354</t>
+          <t>ENSMUSG00000034371</t>
         </is>
       </c>
       <c r="B335" t="inlineStr">
         <is>
-          <t>Slc39a4</t>
+          <t>Tkfc</t>
         </is>
       </c>
       <c r="C335" t="n">
-        <v>-0.9926</v>
+        <v>-0.6889999999999999</v>
       </c>
       <c r="D335" t="n">
-        <v>0.000147</v>
+        <v>7.8e-05</v>
       </c>
     </row>
     <row r="336">
       <c r="A336" t="inlineStr">
         <is>
-          <t>ENSMUSG00000063558</t>
+          <t>ENSMUSG00000021957</t>
         </is>
       </c>
       <c r="B336" t="inlineStr">
         <is>
-          <t>Aox1</t>
+          <t>Tkt</t>
         </is>
       </c>
       <c r="C336" t="n">
-        <v>-1.2065</v>
+        <v>-0.6192</v>
       </c>
       <c r="D336" t="n">
-        <v>0.010722</v>
+        <v>0.000967</v>
       </c>
     </row>
     <row r="337">
       <c r="A337" t="inlineStr">
         <is>
-          <t>ENSMUSG00000063704</t>
+          <t>ENSMUSG00000029810</t>
         </is>
       </c>
       <c r="B337" t="inlineStr">
         <is>
-          <t>Mapk15</t>
+          <t>Tmem176b</t>
         </is>
       </c>
       <c r="C337" t="n">
-        <v>-1.577</v>
+        <v>0.8260999999999999</v>
       </c>
       <c r="D337" t="n">
-        <v>0</v>
+        <v>0.001258</v>
       </c>
     </row>
     <row r="338">
       <c r="A338" t="inlineStr">
         <is>
-          <t>ENSMUSG00000063919</t>
+          <t>ENSMUSG00000042305</t>
         </is>
       </c>
       <c r="B338" t="inlineStr">
         <is>
-          <t>Srrm4</t>
+          <t>Tmem183a</t>
         </is>
       </c>
       <c r="C338" t="n">
-        <v>2.8102</v>
+        <v>-1.1959</v>
       </c>
       <c r="D338" t="n">
-        <v>0.000125</v>
+        <v>0.008946000000000001</v>
       </c>
     </row>
     <row r="339">
       <c r="A339" t="inlineStr">
         <is>
-          <t>ENSMUSG00000064254</t>
+          <t>ENSMUSG00000032091</t>
         </is>
       </c>
       <c r="B339" t="inlineStr">
         <is>
-          <t>Ethe1</t>
+          <t>Tmprss4</t>
         </is>
       </c>
       <c r="C339" t="n">
-        <v>-0.602</v>
+        <v>5.6186</v>
       </c>
       <c r="D339" t="n">
-        <v>0.006389</v>
+        <v>0.000145</v>
       </c>
     </row>
     <row r="340">
       <c r="A340" t="inlineStr">
         <is>
-          <t>ENSMUSG00000064363</t>
+          <t>ENSMUSG00000034723</t>
         </is>
       </c>
       <c r="B340" t="inlineStr">
         <is>
-          <t>mt-Nd4</t>
+          <t>Tmx4</t>
         </is>
       </c>
       <c r="C340" t="n">
-        <v>0.8316</v>
+        <v>-1.6054</v>
       </c>
       <c r="D340" t="n">
-        <v>0.032154</v>
+        <v>0.041204</v>
       </c>
     </row>
     <row r="341">
       <c r="A341" t="inlineStr">
         <is>
-          <t>ENSMUSG00000066071</t>
+          <t>ENSMUSG00000055322</t>
         </is>
       </c>
       <c r="B341" t="inlineStr">
         <is>
-          <t>Cyp4a12a</t>
+          <t>Tns1</t>
         </is>
       </c>
       <c r="C341" t="n">
-        <v>-2.009</v>
+        <v>-1.0308</v>
       </c>
       <c r="D341" t="n">
-        <v>0.045033</v>
+        <v>7.499999999999999e-05</v>
       </c>
     </row>
     <row r="342">
       <c r="A342" t="inlineStr">
         <is>
-          <t>ENSMUSG00000066149</t>
+          <t>ENSMUSG00000051682</t>
         </is>
       </c>
       <c r="B342" t="inlineStr">
         <is>
-          <t>Cdc26</t>
+          <t>Treml4</t>
         </is>
       </c>
       <c r="C342" t="n">
-        <v>-4.729</v>
+        <v>1.6583</v>
       </c>
       <c r="D342" t="n">
-        <v>0.000147</v>
+        <v>0.032154</v>
       </c>
     </row>
     <row r="343">
       <c r="A343" t="inlineStr">
         <is>
-          <t>ENSMUSG00000066154</t>
+          <t>ENSMUSG00000032501</t>
         </is>
       </c>
       <c r="B343" t="inlineStr">
         <is>
-          <t>Mup3</t>
+          <t>Trib1</t>
         </is>
       </c>
       <c r="C343" t="n">
-        <v>-0.9781</v>
+        <v>0.6657999999999999</v>
       </c>
       <c r="D343" t="n">
-        <v>0.044533</v>
+        <v>0.002789</v>
       </c>
     </row>
     <row r="344">
       <c r="A344" t="inlineStr">
         <is>
-          <t>ENSMUSG00000067071</t>
+          <t>ENSMUSG00000025511</t>
         </is>
       </c>
       <c r="B344" t="inlineStr">
         <is>
-          <t>Hes6</t>
+          <t>Tspan4</t>
         </is>
       </c>
       <c r="C344" t="n">
-        <v>-1.2844</v>
+        <v>0.8984</v>
       </c>
       <c r="D344" t="n">
-        <v>0</v>
+        <v>0.002789</v>
       </c>
     </row>
     <row r="345">
       <c r="A345" t="inlineStr">
         <is>
-          <t>ENSMUSG00000067225</t>
+          <t>ENSMUSG00000103711</t>
         </is>
       </c>
       <c r="B345" t="inlineStr">
         <is>
-          <t>Cyp2c54</t>
+          <t>Tstd1</t>
         </is>
       </c>
       <c r="C345" t="n">
-        <v>0.8713</v>
+        <v>0.9731</v>
       </c>
       <c r="D345" t="n">
-        <v>0.002286</v>
+        <v>0.005649</v>
       </c>
     </row>
     <row r="346">
       <c r="A346" t="inlineStr">
         <is>
-          <t>ENSMUSG00000068086</t>
+          <t>ENSMUSG00000028555</t>
         </is>
       </c>
       <c r="B346" t="inlineStr">
         <is>
-          <t>Cyp2d9</t>
+          <t>Ttc39a</t>
         </is>
       </c>
       <c r="C346" t="n">
-        <v>-1.2312</v>
+        <v>2.9232</v>
       </c>
       <c r="D346" t="n">
-        <v>0.019509</v>
+        <v>0.020085</v>
       </c>
     </row>
     <row r="347">
       <c r="A347" t="inlineStr">
         <is>
-          <t>ENSMUSG00000068299</t>
+          <t>ENSMUSG00000061808</t>
         </is>
       </c>
       <c r="B347" t="inlineStr">
         <is>
-          <t>Nat8f4</t>
+          <t>Ttr</t>
         </is>
       </c>
       <c r="C347" t="n">
-        <v>1.0956</v>
+        <v>-0.7374000000000001</v>
       </c>
       <c r="D347" t="n">
-        <v>0.011935</v>
+        <v>3.7e-05</v>
       </c>
     </row>
     <row r="348">
       <c r="A348" t="inlineStr">
         <is>
-          <t>ENSMUSG00000068566</t>
+          <t>ENSMUSG00000058672</t>
         </is>
       </c>
       <c r="B348" t="inlineStr">
         <is>
-          <t>Myadm</t>
+          <t>Tubb2a</t>
         </is>
       </c>
       <c r="C348" t="n">
-        <v>0.8206</v>
+        <v>-1.2794</v>
       </c>
       <c r="D348" t="n">
-        <v>0.024819</v>
+        <v>0.00058</v>
       </c>
     </row>
     <row r="349">
       <c r="A349" t="inlineStr">
         <is>
-          <t>ENSMUSG00000068762</t>
+          <t>ENSMUSG00000036752</t>
         </is>
       </c>
       <c r="B349" t="inlineStr">
         <is>
-          <t>Gstm6</t>
+          <t>Tubb4b</t>
         </is>
       </c>
       <c r="C349" t="n">
-        <v>-1.0043</v>
+        <v>-0.6359</v>
       </c>
       <c r="D349" t="n">
-        <v>0.000459</v>
+        <v>0.024564</v>
       </c>
     </row>
     <row r="350">
       <c r="A350" t="inlineStr">
         <is>
-          <t>ENSMUSG00000070645</t>
+          <t>ENSMUSG00000118664</t>
         </is>
       </c>
       <c r="B350" t="inlineStr">
         <is>
-          <t>Ren1</t>
+          <t>Tusc3</t>
         </is>
       </c>
       <c r="C350" t="n">
-        <v>8.276999999999999</v>
+        <v>-1.1814</v>
       </c>
       <c r="D350" t="n">
-        <v>0</v>
+        <v>0.010615</v>
       </c>
     </row>
     <row r="351">
       <c r="A351" t="inlineStr">
         <is>
-          <t>ENSMUSG00000071076</t>
+          <t>ENSMUSG00000030579</t>
         </is>
       </c>
       <c r="B351" t="inlineStr">
         <is>
-          <t>Jund</t>
+          <t>Tyrobp</t>
         </is>
       </c>
       <c r="C351" t="n">
-        <v>0.534</v>
+        <v>0.9735</v>
       </c>
       <c r="D351" t="n">
-        <v>0.028953</v>
+        <v>0.000238</v>
       </c>
     </row>
     <row r="352">
       <c r="A352" t="inlineStr">
         <is>
-          <t>ENSMUSG00000071172</t>
+          <t>ENSMUSG00000020634</t>
         </is>
       </c>
       <c r="B352" t="inlineStr">
         <is>
-          <t>Srsf3</t>
+          <t>Ubxn2a</t>
         </is>
       </c>
       <c r="C352" t="n">
-        <v>0.871</v>
+        <v>-0.6092</v>
       </c>
       <c r="D352" t="n">
-        <v>0.019236</v>
+        <v>0.002179</v>
       </c>
     </row>
     <row r="353">
       <c r="A353" t="inlineStr">
         <is>
-          <t>ENSMUSG00000071551</t>
+          <t>ENSMUSG00000035836</t>
         </is>
       </c>
       <c r="B353" t="inlineStr">
         <is>
-          <t>Akr1c19</t>
+          <t>Ugt2b1</t>
         </is>
       </c>
       <c r="C353" t="n">
-        <v>-2.2414</v>
+        <v>-1.2677</v>
       </c>
       <c r="D353" t="n">
-        <v>0.000226</v>
+        <v>0.005529</v>
       </c>
     </row>
     <row r="354">
       <c r="A354" t="inlineStr">
         <is>
-          <t>ENSMUSG00000071637</t>
+          <t>ENSMUSG00000035811</t>
         </is>
       </c>
       <c r="B354" t="inlineStr">
         <is>
-          <t>Cebpd</t>
+          <t>Ugt2b35</t>
         </is>
       </c>
       <c r="C354" t="n">
-        <v>1.5735</v>
+        <v>-0.6855</v>
       </c>
       <c r="D354" t="n">
-        <v>0.000327</v>
+        <v>0.01044</v>
       </c>
     </row>
     <row r="355">
       <c r="A355" t="inlineStr">
         <is>
-          <t>ENSMUSG00000071715</t>
+          <t>ENSMUSG00000051748</t>
         </is>
       </c>
       <c r="B355" t="inlineStr">
         <is>
-          <t>Ncf4</t>
+          <t>Wfdc21</t>
         </is>
       </c>
       <c r="C355" t="n">
-        <v>1.5477</v>
+        <v>0.7135</v>
       </c>
       <c r="D355" t="n">
-        <v>0.006235</v>
+        <v>0.012009</v>
       </c>
     </row>
     <row r="356">
       <c r="A356" t="inlineStr">
         <is>
-          <t>ENSMUSG00000072115</t>
+          <t>ENSMUSG00000028639</t>
         </is>
       </c>
       <c r="B356" t="inlineStr">
         <is>
-          <t>Ang</t>
+          <t>Ybx1</t>
         </is>
       </c>
       <c r="C356" t="n">
-        <v>1.3453</v>
+        <v>-0.707</v>
       </c>
       <c r="D356" t="n">
-        <v>1e-05</v>
+        <v>0.041041</v>
       </c>
     </row>
     <row r="357">
       <c r="A357" t="inlineStr">
         <is>
-          <t>ENSMUSG00000072872</t>
+          <t>ENSMUSG00000026117</t>
         </is>
       </c>
       <c r="B357" t="inlineStr">
         <is>
-          <t>Rybp</t>
+          <t>Zap70</t>
         </is>
       </c>
       <c r="C357" t="n">
-        <v>-2.4153</v>
+        <v>1.2308</v>
       </c>
       <c r="D357" t="n">
-        <v>0.012227</v>
+        <v>0.004575</v>
       </c>
     </row>
     <row r="358">
       <c r="A358" t="inlineStr">
         <is>
-          <t>ENSMUSG00000072941</t>
+          <t>ENSMUSG00000027514</t>
         </is>
       </c>
       <c r="B358" t="inlineStr">
         <is>
-          <t>Sod3</t>
+          <t>Zbp1</t>
         </is>
       </c>
       <c r="C358" t="n">
-        <v>0.5672</v>
+        <v>0.907</v>
       </c>
       <c r="D358" t="n">
-        <v>0.044801</v>
+        <v>0.04916</v>
       </c>
     </row>
     <row r="359">
       <c r="A359" t="inlineStr">
         <is>
-          <t>ENSMUSG00000073418</t>
+          <t>ENSMUSG00000027091</t>
         </is>
       </c>
       <c r="B359" t="inlineStr">
         <is>
-          <t>C4b</t>
+          <t>Zc3h15</t>
         </is>
       </c>
       <c r="C359" t="n">
-        <v>0.7601</v>
+        <v>-0.5835</v>
       </c>
       <c r="D359" t="n">
-        <v>0.007243</v>
+        <v>0.034906</v>
       </c>
     </row>
     <row r="360">
       <c r="A360" t="inlineStr">
         <is>
-          <t>ENSMUSG00000073609</t>
+          <t>ENSMUSG00000044786</t>
         </is>
       </c>
       <c r="B360" t="inlineStr">
         <is>
-          <t>D2hgdh</t>
+          <t>Zfp36</t>
         </is>
       </c>
       <c r="C360" t="n">
-        <v>-1.14</v>
+        <v>0.8459</v>
       </c>
       <c r="D360" t="n">
-        <v>0.032154</v>
+        <v>0.000677</v>
       </c>
     </row>
     <row r="361">
       <c r="A361" t="inlineStr">
         <is>
-          <t>ENSMUSG00000074064</t>
+          <t>ENSMUSG00000021510</t>
         </is>
       </c>
       <c r="B361" t="inlineStr">
         <is>
-          <t>Mlycd</t>
+          <t>Zfp729a</t>
         </is>
       </c>
       <c r="C361" t="n">
-        <v>0.5394</v>
+        <v>-4.1645</v>
       </c>
       <c r="D361" t="n">
-        <v>0.012227</v>
+        <v>0.001651</v>
       </c>
     </row>
     <row r="362">
       <c r="A362" t="inlineStr">
         <is>
-          <t>ENSMUSG00000074115</t>
+          <t>ENSMUSG00000044068</t>
         </is>
       </c>
       <c r="B362" t="inlineStr">
         <is>
-          <t>Saa1</t>
+          <t>Zrsr1</t>
         </is>
       </c>
       <c r="C362" t="n">
-        <v>4.1014</v>
+        <v>-0.9405</v>
       </c>
       <c r="D362" t="n">
-        <v>0.005165</v>
+        <v>0.006308</v>
       </c>
     </row>
     <row r="363">
       <c r="A363" t="inlineStr">
         <is>
-          <t>ENSMUSG00000074639</t>
+          <t>ENSMUSG00000064363</t>
         </is>
       </c>
       <c r="B363" t="inlineStr">
         <is>
-          <t>Rdh16f2</t>
+          <t>mt-Nd4</t>
         </is>
       </c>
       <c r="C363" t="n">
-        <v>0.6189</v>
+        <v>0.8316</v>
       </c>
       <c r="D363" t="n">
-        <v>0.041586</v>
+        <v>0.032154</v>
       </c>
     </row>
     <row r="364">
       <c r="A364" t="inlineStr">
         <is>
-          <t>ENSMUSG00000076609</t>
+          <t>10:41404000</t>
         </is>
       </c>
       <c r="B364" t="inlineStr">
         <is>
-          <t>Igkc</t>
+          <t>unannotated</t>
         </is>
       </c>
       <c r="C364" t="n">
-        <v>3.0166</v>
+        <v>-5.2845</v>
       </c>
       <c r="D364" t="n">
-        <v>0</v>
+        <v>0.017225</v>
       </c>
     </row>
     <row r="365">
       <c r="A365" t="inlineStr">
         <is>
-          <t>ENSMUSG00000076612</t>
+          <t>11:116060000</t>
         </is>
       </c>
       <c r="B365" t="inlineStr">
         <is>
-          <t>Ighg2c</t>
+          <t>unannotated</t>
         </is>
       </c>
       <c r="C365" t="n">
-        <v>3.8731</v>
+        <v>0.8257</v>
       </c>
       <c r="D365" t="n">
-        <v>0</v>
+        <v>0.002619</v>
       </c>
     </row>
     <row r="366">
       <c r="A366" t="inlineStr">
         <is>
-          <t>ENSMUSG00000076613</t>
+          <t>11:5470000</t>
         </is>
       </c>
       <c r="B366" t="inlineStr">
         <is>
-          <t>Ighg2b</t>
+          <t>unannotated</t>
         </is>
       </c>
       <c r="C366" t="n">
-        <v>3.7499</v>
+        <v>6.1401</v>
       </c>
       <c r="D366" t="n">
-        <v>0</v>
+        <v>0.000672</v>
       </c>
     </row>
     <row r="367">
       <c r="A367" t="inlineStr">
         <is>
-          <t>ENSMUSG00000076614</t>
+          <t>11:83463000</t>
         </is>
       </c>
       <c r="B367" t="inlineStr">
         <is>
-          <t>Ighg1</t>
+          <t>unannotated</t>
         </is>
       </c>
       <c r="C367" t="n">
-        <v>3.4313</v>
+        <v>1.0772</v>
       </c>
       <c r="D367" t="n">
-        <v>0.005524</v>
+        <v>0.010641</v>
       </c>
     </row>
     <row r="368">
       <c r="A368" t="inlineStr">
         <is>
-          <t>ENSMUSG00000078672</t>
+          <t>12:104360000</t>
         </is>
       </c>
       <c r="B368" t="inlineStr">
         <is>
-          <t>Mup20</t>
+          <t>unannotated</t>
         </is>
       </c>
       <c r="C368" t="n">
-        <v>-1.7554</v>
+        <v>1.1664</v>
       </c>
       <c r="D368" t="n">
-        <v>1e-06</v>
+        <v>0.029745</v>
       </c>
     </row>
     <row r="369">
       <c r="A369" t="inlineStr">
         <is>
-          <t>ENSMUSG00000078931</t>
+          <t>12:104361000</t>
         </is>
       </c>
       <c r="B369" t="inlineStr">
         <is>
-          <t>Pdf</t>
+          <t>unannotated</t>
         </is>
       </c>
       <c r="C369" t="n">
-        <v>-6.0704</v>
+        <v>1.7688</v>
       </c>
       <c r="D369" t="n">
-        <v>0.009920999999999999</v>
+        <v>0.001884</v>
       </c>
     </row>
     <row r="370">
       <c r="A370" t="inlineStr">
         <is>
-          <t>ENSMUSG00000079362</t>
+          <t>14:30625000</t>
         </is>
       </c>
       <c r="B370" t="inlineStr">
         <is>
-          <t>Gm43302</t>
+          <t>unannotated</t>
         </is>
       </c>
       <c r="C370" t="n">
-        <v>6.4366</v>
+        <v>1.9458</v>
       </c>
       <c r="D370" t="n">
-        <v>0.003796</v>
+        <v>0.013112</v>
       </c>
     </row>
     <row r="371">
       <c r="A371" t="inlineStr">
         <is>
-          <t>ENSMUSG00000081642</t>
+          <t>14:46322000</t>
         </is>
       </c>
       <c r="B371" t="inlineStr">
         <is>
-          <t>Gm13532</t>
+          <t>unannotated</t>
         </is>
       </c>
       <c r="C371" t="n">
-        <v>1.2203</v>
+        <v>1.227</v>
       </c>
       <c r="D371" t="n">
-        <v>1.4e-05</v>
+        <v>0</v>
       </c>
     </row>
     <row r="372">
       <c r="A372" t="inlineStr">
         <is>
-          <t>ENSMUSG00000086054</t>
+          <t>16:30075000</t>
         </is>
       </c>
       <c r="B372" t="inlineStr">
         <is>
-          <t>Hnf1aos1</t>
+          <t>unannotated</t>
         </is>
       </c>
       <c r="C372" t="n">
-        <v>-1.3606</v>
+        <v>0.5738</v>
       </c>
       <c r="D372" t="n">
-        <v>0.015193</v>
+        <v>0.000342</v>
       </c>
     </row>
     <row r="373">
       <c r="A373" t="inlineStr">
         <is>
-          <t>ENSMUSG00000089694</t>
+          <t>16:91882000</t>
         </is>
       </c>
       <c r="B373" t="inlineStr">
         <is>
-          <t>Nat8f7</t>
+          <t>unannotated</t>
         </is>
       </c>
       <c r="C373" t="n">
-        <v>4.3763</v>
+        <v>-2.3586</v>
       </c>
       <c r="D373" t="n">
-        <v>0.021096</v>
+        <v>0.043947</v>
       </c>
     </row>
     <row r="374">
       <c r="A374" t="inlineStr">
         <is>
-          <t>ENSMUSG00000090231</t>
+          <t>17:85372000</t>
         </is>
       </c>
       <c r="B374" t="inlineStr">
         <is>
-          <t>Cfb</t>
+          <t>unannotated</t>
         </is>
       </c>
       <c r="C374" t="n">
-        <v>0.6953</v>
+        <v>1.4365</v>
       </c>
       <c r="D374" t="n">
-        <v>0.007775</v>
+        <v>0.001886</v>
       </c>
     </row>
     <row r="375">
       <c r="A375" t="inlineStr">
         <is>
-          <t>ENSMUSG00000090877</t>
+          <t>18:20799000</t>
         </is>
       </c>
       <c r="B375" t="inlineStr">
         <is>
-          <t>Hspa1b</t>
+          <t>unannotated</t>
         </is>
       </c>
       <c r="C375" t="n">
-        <v>-0.9762</v>
+        <v>-1.4435</v>
       </c>
       <c r="D375" t="n">
-        <v>0.002005</v>
+        <v>0</v>
       </c>
     </row>
     <row r="376">
       <c r="A376" t="inlineStr">
         <is>
-          <t>ENSMUSG00000092274</t>
+          <t>19:39595000</t>
         </is>
       </c>
       <c r="B376" t="inlineStr">
         <is>
-          <t>Neat1</t>
+          <t>unannotated</t>
         </is>
       </c>
       <c r="C376" t="n">
-        <v>1.0489</v>
+        <v>-1.1657</v>
       </c>
       <c r="D376" t="n">
-        <v>0.00572</v>
+        <v>1e-05</v>
       </c>
     </row>
     <row r="377">
       <c r="A377" t="inlineStr">
         <is>
-          <t>ENSMUSG00000093483</t>
+          <t>19:5506000</t>
         </is>
       </c>
       <c r="B377" t="inlineStr">
         <is>
-          <t>AA465934</t>
+          <t>unannotated</t>
         </is>
       </c>
       <c r="C377" t="n">
-        <v>3.0148</v>
+        <v>0.9461000000000001</v>
       </c>
       <c r="D377" t="n">
-        <v>0.032154</v>
+        <v>6.2e-05</v>
       </c>
     </row>
     <row r="378">
       <c r="A378" t="inlineStr">
         <is>
-          <t>ENSMUSG00000095079</t>
+          <t>1:151012000</t>
         </is>
       </c>
       <c r="B378" t="inlineStr">
         <is>
-          <t>Igha</t>
+          <t>unannotated</t>
         </is>
       </c>
       <c r="C378" t="n">
-        <v>3.2498</v>
+        <v>4.9601</v>
       </c>
       <c r="D378" t="n">
-        <v>1.8e-05</v>
+        <v>0</v>
       </c>
     </row>
     <row r="379">
       <c r="A379" t="inlineStr">
         <is>
-          <t>ENSMUSG00000096768</t>
+          <t>1:151017000</t>
         </is>
       </c>
       <c r="B379" t="inlineStr">
         <is>
-          <t>Gm47283</t>
+          <t>unannotated</t>
         </is>
       </c>
       <c r="C379" t="n">
-        <v>3.2947</v>
+        <v>-1.3225</v>
       </c>
       <c r="D379" t="n">
-        <v>0</v>
+        <v>0.029494</v>
       </c>
     </row>
     <row r="380">
       <c r="A380" t="inlineStr">
         <is>
-          <t>ENSMUSG00000102095</t>
+          <t>1:160830000</t>
         </is>
       </c>
       <c r="B380" t="inlineStr">
         <is>
-          <t>C730036E19Rik</t>
+          <t>unannotated</t>
         </is>
       </c>
       <c r="C380" t="n">
-        <v>-5.2658</v>
+        <v>-0.5406</v>
       </c>
       <c r="D380" t="n">
-        <v>0.004986</v>
+        <v>0.039971</v>
       </c>
     </row>
     <row r="381">
       <c r="A381" t="inlineStr">
         <is>
-          <t>ENSMUSG00000103711</t>
+          <t>1:21334000</t>
         </is>
       </c>
       <c r="B381" t="inlineStr">
         <is>
-          <t>Tstd1</t>
+          <t>unannotated</t>
         </is>
       </c>
       <c r="C381" t="n">
-        <v>0.9731</v>
+        <v>-6.7023</v>
       </c>
       <c r="D381" t="n">
-        <v>0.005649</v>
+        <v>1e-06</v>
       </c>
     </row>
     <row r="382">
       <c r="A382" t="inlineStr">
         <is>
-          <t>ENSMUSG00000105837</t>
+          <t>2:22479000</t>
         </is>
       </c>
       <c r="B382" t="inlineStr">
         <is>
-          <t>Gm35986</t>
+          <t>unannotated</t>
         </is>
       </c>
       <c r="C382" t="n">
-        <v>-1.8463</v>
+        <v>3.5133</v>
       </c>
       <c r="D382" t="n">
-        <v>0.001169</v>
+        <v>0.009585</v>
       </c>
     </row>
     <row r="383">
       <c r="A383" t="inlineStr">
         <is>
-          <t>ENSMUSG00000105906</t>
+          <t>2:58680000</t>
         </is>
       </c>
       <c r="B383" t="inlineStr">
         <is>
-          <t>Iglc1</t>
+          <t>unannotated</t>
         </is>
       </c>
       <c r="C383" t="n">
-        <v>2.5617</v>
+        <v>1.1413</v>
       </c>
       <c r="D383" t="n">
-        <v>0.021382</v>
+        <v>0.025449</v>
       </c>
     </row>
     <row r="384">
       <c r="A384" t="inlineStr">
         <is>
-          <t>ENSMUSG00000108763</t>
+          <t>3:40743000</t>
         </is>
       </c>
       <c r="B384" t="inlineStr">
         <is>
-          <t>Gm36028</t>
+          <t>unannotated</t>
         </is>
       </c>
       <c r="C384" t="n">
-        <v>-1.9149</v>
+        <v>-1.1448</v>
       </c>
       <c r="D384" t="n">
-        <v>0.008472</v>
+        <v>0.012227</v>
       </c>
     </row>
     <row r="385">
       <c r="A385" t="inlineStr">
         <is>
-          <t>ENSMUSG00000109482</t>
+          <t>3:82938000</t>
         </is>
       </c>
       <c r="B385" t="inlineStr">
         <is>
-          <t>Gm4756</t>
+          <t>unannotated</t>
         </is>
       </c>
       <c r="C385" t="n">
-        <v>0.6829</v>
+        <v>0.982</v>
       </c>
       <c r="D385" t="n">
-        <v>0.045438</v>
+        <v>0.006696</v>
       </c>
     </row>
     <row r="386">
       <c r="A386" t="inlineStr">
         <is>
-          <t>ENSMUSG00000110156</t>
+          <t>4:144938000</t>
         </is>
       </c>
       <c r="B386" t="inlineStr">
         <is>
-          <t>Gm42067</t>
+          <t>unannotated</t>
         </is>
       </c>
       <c r="C386" t="n">
-        <v>-2.0918</v>
+        <v>5.1477</v>
       </c>
       <c r="D386" t="n">
-        <v>0.022701</v>
+        <v>0.042349</v>
       </c>
     </row>
     <row r="387">
       <c r="A387" t="inlineStr">
         <is>
-          <t>ENSMUSG00000110588</t>
+          <t>4:152416000</t>
         </is>
       </c>
       <c r="B387" t="inlineStr">
         <is>
-          <t>Gm45774</t>
+          <t>unannotated</t>
         </is>
       </c>
       <c r="C387" t="n">
-        <v>4.5927</v>
+        <v>0.7151999999999999</v>
       </c>
       <c r="D387" t="n">
-        <v>0.004436</v>
+        <v>0.01052</v>
       </c>
     </row>
     <row r="388">
       <c r="A388" t="inlineStr">
         <is>
-          <t>ENSMUSG00000111878</t>
+          <t>4:61968000</t>
         </is>
       </c>
       <c r="B388" t="inlineStr">
         <is>
-          <t>Gm47777</t>
+          <t>unannotated</t>
         </is>
       </c>
       <c r="C388" t="n">
-        <v>4.4982</v>
+        <v>-2.3074</v>
       </c>
       <c r="D388" t="n">
-        <v>0.004607</v>
+        <v>0.034848</v>
       </c>
     </row>
     <row r="389">
       <c r="A389" t="inlineStr">
         <is>
-          <t>ENSMUSG00000113047</t>
+          <t>4:6264000</t>
         </is>
       </c>
       <c r="B389" t="inlineStr">
         <is>
-          <t>Gm47469</t>
+          <t>unannotated</t>
         </is>
       </c>
       <c r="C389" t="n">
-        <v>-4.2081</v>
+        <v>-1.3771</v>
       </c>
       <c r="D389" t="n">
-        <v>0.034312</v>
+        <v>0.005365</v>
       </c>
     </row>
     <row r="390">
       <c r="A390" t="inlineStr">
         <is>
-          <t>ENSMUSG00000113529</t>
+          <t>5:113234000</t>
         </is>
       </c>
       <c r="B390" t="inlineStr">
         <is>
-          <t>Gm47484</t>
+          <t>unannotated</t>
         </is>
       </c>
       <c r="C390" t="n">
-        <v>-3.0391</v>
+        <v>0.6432</v>
       </c>
       <c r="D390" t="n">
-        <v>0.036882</v>
+        <v>0.001644</v>
       </c>
     </row>
     <row r="391">
       <c r="A391" t="inlineStr">
         <is>
-          <t>ENSMUSG00000114818</t>
+          <t>7:25924000</t>
         </is>
       </c>
       <c r="B391" t="inlineStr">
         <is>
-          <t>Gm35164</t>
+          <t>unannotated</t>
         </is>
       </c>
       <c r="C391" t="n">
-        <v>3.4839</v>
+        <v>7.4302</v>
       </c>
       <c r="D391" t="n">
-        <v>1e-06</v>
+        <v>2.5e-05</v>
       </c>
     </row>
     <row r="392">
       <c r="A392" t="inlineStr">
         <is>
-          <t>ENSMUSG00000115338</t>
+          <t>7:33900000</t>
         </is>
       </c>
       <c r="B392" t="inlineStr">
         <is>
-          <t>Pnp</t>
+          <t>unannotated</t>
         </is>
       </c>
       <c r="C392" t="n">
-        <v>-0.6788999999999999</v>
+        <v>-0.8692</v>
       </c>
       <c r="D392" t="n">
-        <v>0.025569</v>
+        <v>2e-06</v>
       </c>
     </row>
     <row r="393">
       <c r="A393" t="inlineStr">
         <is>
-          <t>ENSMUSG00000117879</t>
+          <t>7:99306000</t>
         </is>
       </c>
       <c r="B393" t="inlineStr">
         <is>
-          <t>2310015A16Rik</t>
+          <t>unannotated</t>
         </is>
       </c>
       <c r="C393" t="n">
-        <v>3.3752</v>
+        <v>3.8699</v>
       </c>
       <c r="D393" t="n">
-        <v>0</v>
+        <v>0.002164</v>
       </c>
     </row>
     <row r="394">
       <c r="A394" t="inlineStr">
         <is>
-          <t>ENSMUSG00000117912</t>
+          <t>8:129179000</t>
         </is>
       </c>
       <c r="B394" t="inlineStr">
         <is>
-          <t>Gm50383</t>
+          <t>unannotated</t>
         </is>
       </c>
       <c r="C394" t="n">
-        <v>-1.6648</v>
+        <v>1.3992</v>
       </c>
       <c r="D394" t="n">
-        <v>0.0009940000000000001</v>
+        <v>0.015745</v>
       </c>
     </row>
     <row r="395">
       <c r="A395" t="inlineStr">
         <is>
-          <t>ENSMUSG00000118017</t>
+          <t>8:91613000</t>
         </is>
       </c>
       <c r="B395" t="inlineStr">
         <is>
-          <t>Gm29966</t>
+          <t>unannotated</t>
         </is>
       </c>
       <c r="C395" t="n">
-        <v>-0.8469</v>
+        <v>0.9946</v>
       </c>
       <c r="D395" t="n">
-        <v>0.002916</v>
+        <v>0.033505</v>
       </c>
     </row>
     <row r="396">
       <c r="A396" t="inlineStr">
         <is>
-          <t>ENSMUSG00000118664</t>
+          <t>9:107526000</t>
         </is>
       </c>
       <c r="B396" t="inlineStr">
         <is>
-          <t>Tusc3</t>
+          <t>unannotated</t>
         </is>
       </c>
       <c r="C396" t="n">
-        <v>-1.1814</v>
+        <v>0.7813</v>
       </c>
       <c r="D396" t="n">
-        <v>0.010615</v>
+        <v>0.005649</v>
       </c>
     </row>
     <row r="397">
       <c r="A397" t="inlineStr">
         <is>
-          <t>ENSMUSG00000119987</t>
+          <t>9:107551000</t>
         </is>
       </c>
       <c r="B397" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>unannotated</t>
         </is>
       </c>
       <c r="C397" t="n">
-        <v>2.135</v>
+        <v>3.5042</v>
       </c>
       <c r="D397" t="n">
-        <v>0.031238</v>
+        <v>0</v>
       </c>
     </row>
     <row r="398">
       <c r="A398" t="inlineStr">
         <is>
-          <t>ENSMUSG00000120849</t>
+          <t>9:110814000</t>
         </is>
       </c>
       <c r="B398" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>unannotated</t>
         </is>
       </c>
       <c r="C398" t="n">
-        <v>1.0709</v>
+        <v>-9.4314</v>
       </c>
       <c r="D398" t="n">
-        <v>0.015739</v>
+        <v>0</v>
       </c>
     </row>
     <row r="399">
       <c r="A399" t="inlineStr">
         <is>
-          <t>ENSMUSG00000121349</t>
+          <t>9:46140000</t>
         </is>
       </c>
       <c r="B399" t="inlineStr">
         <is>
-          <t>Speer6-ps1</t>
+          <t>unannotated</t>
         </is>
       </c>
       <c r="C399" t="n">
-        <v>0.7079</v>
+        <v>0.9224</v>
       </c>
       <c r="D399" t="n">
-        <v>0.000683</v>
+        <v>0.000218</v>
       </c>
     </row>
     <row r="400">
       <c r="A400" t="inlineStr">
         <is>
-          <t>ENSMUSG00000121473</t>
+          <t>ENSMUSG00000119987</t>
         </is>
       </c>
       <c r="B400" t="inlineStr">
         <is>
-          <t>Adh6-ps1</t>
+          <t>unannotated</t>
         </is>
       </c>
       <c r="C400" t="n">
-        <v>-1.3358</v>
+        <v>2.135</v>
       </c>
       <c r="D400" t="n">
-        <v>0.006178</v>
+        <v>0.031238</v>
       </c>
     </row>
     <row r="401">
       <c r="A401" t="inlineStr">
         <is>
-          <t>ENSMUSG00000121494</t>
+          <t>ENSMUSG00000120849</t>
         </is>
       </c>
       <c r="B401" t="inlineStr">
         <is>
-          <t>9030619P08Rik</t>
+          <t>unannotated</t>
         </is>
       </c>
       <c r="C401" t="n">
-        <v>1.6797</v>
+        <v>1.0709</v>
       </c>
       <c r="D401" t="n">
-        <v>0.010612</v>
+        <v>0.015739</v>
       </c>
     </row>
     <row r="402">
@@ -7658,7 +7658,7 @@
       </c>
       <c r="B402" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>unannotated</t>
         </is>
       </c>
       <c r="C402" t="n">
